--- a/book/src/doc/Libros.xlsx
+++ b/book/src/doc/Libros.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\book\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C598632F-7D51-4B45-9CF4-D67C2FC8E9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E99B59-4081-4D71-AD06-AE2921B8B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
+    <workbookView xWindow="51480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet6 (2)" sheetId="7" r:id="rId7"/>
+    <sheet name="Versiculos" sheetId="7" r:id="rId7"/>
     <sheet name="Limpieza" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -3229,7 +3229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3349,6 +3349,12 @@
       <color rgb="FFD4D4D4"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -3620,12 +3626,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3638,6 +3638,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3722,15 +3728,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>1146634</xdr:colOff>
+          <xdr:colOff>1152525</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>49561</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>1191394</xdr:colOff>
+          <xdr:colOff>1190625</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>210634</xdr:rowOff>
+          <xdr:rowOff>209550</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3762,7 +3768,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="64008" rIns="64008" bIns="64008" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -3790,15 +3796,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>1341398</xdr:colOff>
+          <xdr:colOff>1343025</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>46464</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>2295293</xdr:colOff>
+          <xdr:colOff>2295525</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>204440</xdr:rowOff>
+          <xdr:rowOff>200025</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3830,7 +3836,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="64008" tIns="64008" rIns="64008" bIns="64008" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -4175,9 +4181,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47029742-AAD8-472F-BC3E-40B45BE73627}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:E16"/>
-  <sheetFormatPr defaultColWidth="31.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="31.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4191,7 +4197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
@@ -4205,7 +4211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
@@ -4219,7 +4225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
@@ -4233,7 +4239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
@@ -4247,7 +4253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>19</v>
       </c>
@@ -4261,7 +4267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
@@ -4275,7 +4281,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
@@ -4289,7 +4295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
@@ -4303,7 +4309,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>32</v>
       </c>
@@ -4317,7 +4323,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>36</v>
       </c>
@@ -4331,7 +4337,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
@@ -4345,7 +4351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>42</v>
       </c>
@@ -4359,7 +4365,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
@@ -4373,7 +4379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>49</v>
       </c>
@@ -4387,7 +4393,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>53</v>
       </c>
@@ -4410,13 +4416,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F27F11-965A-4B61-AEC9-E881A4924896}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C150"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>350</v>
       </c>
       <c r="C1" t="str">
@@ -4424,12 +4430,12 @@
         <v>"1": "Yahveh habló a Moisés y a Aarón, diciendo:",</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>IF(B2="","",A1+1)</f>
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>351</v>
       </c>
       <c r="C2" t="str">
@@ -4437,12 +4443,12 @@
         <v>"2": "Cuando uno tenga en la piel de su carne tumor, erupción o mancha blancuzca brillante, y se forme en la piel de su carne como una llaga de lepra, será llevado al sacerdote Aarón o a uno de sus hijos, los sacerdotes.",</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" ref="A3:A66" si="1">IF(B3="","",A2+1)</f>
         <v>3</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>352</v>
       </c>
       <c r="C3" t="str">
@@ -4450,12 +4456,12 @@
         <v>"3": "El sacerdote examinará la llaga en la piel de la carne; si el pelo en la llaga se ha vuelto blanco, y la llaga parece más hundida que la piel de su carne, es llaga de lepra; cuando el sacerdote lo haya comprobado, le declarará impuro.",</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>353</v>
       </c>
       <c r="C4" t="str">
@@ -4463,12 +4469,12 @@
         <v>"4": "Mas si hay en la piel de su carne una mancha blancuzca brillante sin que parezca más hundida que la piel, y sin que el pelo se haya vuelto blanco, el sacerdote recluirá durante siete días al afectado.",</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>354</v>
       </c>
       <c r="C5" t="str">
@@ -4476,12 +4482,12 @@
         <v>"5": "Al séptimo día el sacerdote lo examinará, y si comprueba que la llaga se ha detenido, no se ha extendido por la piel, el sacerdote entonces lo recluirá otros siete días.",</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="25" t="s">
         <v>355</v>
       </c>
       <c r="C6" t="str">
@@ -4489,12 +4495,12 @@
         <v>"6": "Pasados estos siete días, el sacerdote lo examinará nuevamente: si ve que la llaga ha perdido su color y no se ha extendido en la piel, el sacerdote lo declarará puro; no se trata más que de una erupción. Lavará sus vestidos y quedará puro.",</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="25" t="s">
         <v>356</v>
       </c>
       <c r="C7" t="str">
@@ -4502,12 +4508,12 @@
         <v>"7": "Pero si después que el sacerdote le ha examinado y declarado puro, sigue la erupción extendiéndose por la piel, se presentará de nuevo al sacerdote.",</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="25" t="s">
         <v>357</v>
       </c>
       <c r="C8" t="str">
@@ -4515,12 +4521,12 @@
         <v>"8": "El sacerdote, al comprobar que la erupción se extiende por la piel, lo declarará impuro: es un caso de lepra.",</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="25" t="s">
         <v>358</v>
       </c>
       <c r="C9" t="str">
@@ -4528,12 +4534,12 @@
         <v>"9": "Cuando en un hombre se manifieste una llaga como de lepra, será llevado al sacerdote.",</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>359</v>
       </c>
       <c r="C10" t="str">
@@ -4541,12 +4547,12 @@
         <v>"10": "El sacerdote lo examinará, y si observa un tumor blancuzco en la piel, el color del pelo mudado en blanco y una úlcera en la hinchazón,",</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>360</v>
       </c>
       <c r="C11" t="str">
@@ -4554,12 +4560,12 @@
         <v>"11": "se trata de lepra arraigada en su piel; el sacerdote lo declarará impuro y no le recluirá, porque es impuro.",</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="25" t="s">
         <v>361</v>
       </c>
       <c r="C12" t="str">
@@ -4567,12 +4573,12 @@
         <v>"12": "Pero si la lepra se ha extendido por la piel hasta cubrir toda la piel del enfermo desde la cabeza hasta los pies, en cuanto alcanza a verlo el sacerdote,",</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>362</v>
       </c>
       <c r="C13" t="str">
@@ -4580,12 +4586,12 @@
         <v>"13": "éste lo examinará, y si la lepra ha cubierto toda su carne, declarará puro al afectado por la llaga: se ha vuelto todo blanco; es puro.",</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="25" t="s">
         <v>363</v>
       </c>
       <c r="C14" t="str">
@@ -4593,12 +4599,12 @@
         <v>"14": "Pero cuando se vea en él una úlcera, quedará impuro;",</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="25" t="s">
         <v>364</v>
       </c>
       <c r="C15" t="str">
@@ -4606,12 +4612,12 @@
         <v>"15": "en cuanto el sacerdote vea la úlcera, lo declarará impuro. La úlcera es impura; es un caso de lepra.",</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="25" t="s">
         <v>365</v>
       </c>
       <c r="C16" t="str">
@@ -4619,12 +4625,12 @@
         <v>"16": "Pero si la úlcera cambia, volviéndose blanca, el afectado ha de presentarse al sacerdote.",</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="25" t="s">
         <v>366</v>
       </c>
       <c r="C17" t="str">
@@ -4632,12 +4638,12 @@
         <v>"17": "El sacerdote lo examinará, y al ver que la llaga se ha vuelto blanca, declarará puro al afectado por la enfermedad: es puro.",</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="25" t="s">
         <v>367</v>
       </c>
       <c r="C18" t="str">
@@ -4645,12 +4651,12 @@
         <v>"18": "Cuando en la piel de alguno se ha curado un divieso,",</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="25" t="s">
         <v>368</v>
       </c>
       <c r="C19" t="str">
@@ -4658,12 +4664,12 @@
         <v>"19": "y en el lugar del divieso aparece un tumor blanco, o una mancha de color blanco rojizo, ése habrá de presentarse al sacerdote.",</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="25" t="s">
         <v>369</v>
       </c>
       <c r="C20" t="str">
@@ -4671,12 +4677,12 @@
         <v>"20": "El sacerdote lo examinará, y si la mancha parece más hundida que la piel y su pelo se ha vuelto blanco, el sacerdote lo declarará impuro. Es llaga de lepra que se ha producido en el divieso.",</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>370</v>
       </c>
       <c r="C21" t="str">
@@ -4684,12 +4690,12 @@
         <v>"21": "Pero si el sacerdote ve que no hay en ella pelo blanco, ni está más hundida que la piel, y que ha perdido color, le recluirá por siete días.",</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="25" t="s">
         <v>371</v>
       </c>
       <c r="C22" t="str">
@@ -4697,12 +4703,12 @@
         <v>"22": "Si entonces se extiende por la piel, el sacerdote lo declarará impuro; es un caso de lepra.",</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="25" t="s">
         <v>372</v>
       </c>
       <c r="C23" t="str">
@@ -4710,12 +4716,12 @@
         <v>"23": "Pero si la mancha sigue estacionaria, sin extenderse, es la cicatriz del divieso; el sacerdote lo declarará puro.",</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="25" t="s">
         <v>373</v>
       </c>
       <c r="C24" t="str">
@@ -4723,12 +4729,12 @@
         <v>"24": "Cuando en la piel de alguien hay una quemadura, y sobre la quemadura se forma una mancha de color blanco rojizo o sólo blanco,",</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="25" t="s">
         <v>374</v>
       </c>
       <c r="C25" t="str">
@@ -4736,12 +4742,12 @@
         <v>"25": "el sacerdote la examinará; y si el pelo se ha vuelto blanco en la mancha blanca y ésta aparece más hundida que la piel, es que se ha producido lepra en la quemadura. El sacerdote lo declarará impuro; es un caso de lepra.",</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="25" t="s">
         <v>375</v>
       </c>
       <c r="C26" t="str">
@@ -4749,12 +4755,12 @@
         <v>"26": "Si, en cambio, el sacerdote observa que en la mancha no aparece pelo blanco, que no está más hundida que la piel y que ha perdido color, lo recluirá siete días.",</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="25" t="s">
         <v>376</v>
       </c>
       <c r="C27" t="str">
@@ -4762,12 +4768,12 @@
         <v>"27": "Al séptimo día lo examinará, y si se ha extendido por la piel, el sacerdote lo declarará impuro; es un caso de lepra.",</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>377</v>
       </c>
       <c r="C28" t="str">
@@ -4775,12 +4781,12 @@
         <v>"28": "Pero si la mancha sigue estacionaria sin extenderse por la piel y ha perdido color, se trata de la hinchazón de la quemadura, y el sacerdote lo declarará puro; pues es la cicatriz de la quemadura.",</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="25" t="s">
         <v>378</v>
       </c>
       <c r="C29" t="str">
@@ -4788,12 +4794,12 @@
         <v>"29": "Cuando un hombre o una mujer tengan una llaga en la cabeza o en la barbilla,",</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="25" t="s">
         <v>379</v>
       </c>
       <c r="C30" t="str">
@@ -4801,12 +4807,12 @@
         <v>"30": "el sacerdote examinará la llaga, y si ésta aparece más hundida que la piel, y si hay en ella pelo amarillento y más ralo, el sacerdote lo declarará impuro; es tiña, o sea, lepra de la cabeza o de la barbilla.",</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="25" t="s">
         <v>380</v>
       </c>
       <c r="C31" t="str">
@@ -4814,12 +4820,12 @@
         <v>"31": "Mas si el sacerdote ve que la llaga de tiña no aparece más hundida que la piel, y que no hay en ella pelo amarillento, recluirá al afectado por la tiña durante siete días.",</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="25" t="s">
         <v>381</v>
       </c>
       <c r="C32" t="str">
@@ -4827,12 +4833,12 @@
         <v>"32": "Al séptimo, el sacerdote examinará el mal, y si no se ha extendido la tiña, ni hay en ella pelo amarillento, ni la llaga aparece más hundida que la piel,",</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="25" t="s">
         <v>382</v>
       </c>
       <c r="C33" t="str">
@@ -4840,12 +4846,12 @@
         <v>"33": "aquella persona se afeitará, excepto en el lugar de la tiña; y el sacerdote recluirá al afectado durante otros siete días.",</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="25" t="s">
         <v>383</v>
       </c>
       <c r="C34" t="str">
@@ -4853,12 +4859,12 @@
         <v>"34": "Al séptimo día el sacerdote lo examinará y si no se ha extendido la llaga por la piel, ni aparece más hundida que la piel, le declarará puro; lavará sus vestidos y quedará puro.",</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="25" t="s">
         <v>384</v>
       </c>
       <c r="C35" t="str">
@@ -4866,12 +4872,12 @@
         <v>"35": "Pero si la tiña, después de la purificación, se extiende mucho por la piel,",</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="25" t="s">
         <v>385</v>
       </c>
       <c r="C36" t="str">
@@ -4879,12 +4885,12 @@
         <v>"36": "el sacerdote lo examinará. Si comprueba que la tiña se ha extendido por la piel, el sacerdote ya no tendrá que buscar pelo amarillento; aquella persona es impura.",</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="25" t="s">
         <v>386</v>
       </c>
       <c r="C37" t="str">
@@ -4892,12 +4898,12 @@
         <v>"37": "Mas si, según su opinión, la tiña no se ha extendido y ha brotado en ella pelo negro, se ha curado la tiña. Esa persona es pura y el sacerdote la declarará pura.",</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="25" t="s">
         <v>387</v>
       </c>
       <c r="C38" t="str">
@@ -4905,12 +4911,12 @@
         <v>"38": "Cuando un hombre o una mujer tengan en su piel manchas brillantes, manchas blancas,",</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="25" t="s">
         <v>388</v>
       </c>
       <c r="C39" t="str">
@@ -4918,12 +4924,12 @@
         <v>"39": "el sacerdote las examinará; si comprueba que las manchas de la piel son de color blanco, se trata de un eccema que ha brotado en la piel; esta persona es pura.",</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="25" t="s">
         <v>389</v>
       </c>
       <c r="C40" t="str">
@@ -4931,12 +4937,12 @@
         <v>"40": "Si a alguno se le cae el pelo de la cabeza y queda calvo por detrás, es puro.",</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="25" t="s">
         <v>390</v>
       </c>
       <c r="C41" t="str">
@@ -4944,12 +4950,12 @@
         <v>"41": "Si se le cae el pelo de la parte delantera de la cabeza, es calvo por delante, pero es puro.",</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="25" t="s">
         <v>391</v>
       </c>
       <c r="C42" t="str">
@@ -4957,12 +4963,12 @@
         <v>"42": "Pero si en la calva, por detrás o por delante, aparece una llaga de color rojizo, es lepra que se ha producido en la calva, sea por detrás o por delante.",</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="25" t="s">
         <v>392</v>
       </c>
       <c r="C43" t="str">
@@ -4970,12 +4976,12 @@
         <v>"43": "El sacerdote la examinará y si la hinchazón de la llaga en la parte calva es de color blanco rojizo, con aspecto de lepra en la piel,",</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="25" t="s">
         <v>393</v>
       </c>
       <c r="C44" t="str">
@@ -4983,12 +4989,12 @@
         <v>"44": "se trata de un leproso: es impuro. El sacerdote le declarará impuro; tiene lepra en la cabeza.",</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="25" t="s">
         <v>394</v>
       </c>
       <c r="C45" t="str">
@@ -4996,12 +5002,12 @@
         <v>"45": "El afectado por la lepra llevará los vestido rasgados y desgreñada la cabeza, se cubrirá hasta el bigote e irá gritando: «¡Impuro, impuro!»",</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="25" t="s">
         <v>395</v>
       </c>
       <c r="C46" t="str">
@@ -5009,12 +5015,12 @@
         <v>"46": "Todo el tiempo que dure la llaga, quedará impuro. Es impuro y habitará solo; fuera del campamento tendrá su morada.",</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="25" t="s">
         <v>396</v>
       </c>
       <c r="C47" t="str">
@@ -5022,12 +5028,12 @@
         <v>"47": "Cuando aparezca una llaga de lepra en un vestido de lana o de lino,",</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="25" t="s">
         <v>397</v>
       </c>
       <c r="C48" t="str">
@@ -5035,12 +5041,12 @@
         <v>"48": "o en tejido o cobertor de lino o lana, o en una piel, o en cualquier objeto de cuero,",</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="25" t="s">
         <v>398</v>
       </c>
       <c r="C49" t="str">
@@ -5048,12 +5054,12 @@
         <v>"49": "si la mancha en el vestido o en la piel, o en el tejido o en el cobertor, o en cualquier objeto hecho de cuero, tiene color verdoso o rojizo, es llaga de lepra y debe ser mostrada al sacerdote.",</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="25" t="s">
         <v>399</v>
       </c>
       <c r="C50" t="str">
@@ -5061,12 +5067,12 @@
         <v>"50": "El sacerdote examinará la mancha y encerrará el objeto manchado durante siete días.",</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="25" t="s">
         <v>400</v>
       </c>
       <c r="C51" t="str">
@@ -5074,12 +5080,12 @@
         <v>"51": "Al séptimo, el sacerdote examinará la mancha y si se ha extendido por el vestido, tejido, cobertor, piel o por un objeto de cuero, es un caso de lepra maligna y el objeto es impuro.",</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="25" t="s">
         <v>401</v>
       </c>
       <c r="C52" t="str">
@@ -5087,12 +5093,12 @@
         <v>"52": "Se quemará el vestido, tejido, cobertor de lana o de lino o el objeto de cuero en que se encuentre la mancha, pues es lepra maligna; será quemado.",</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="25" t="s">
         <v>402</v>
       </c>
       <c r="C53" t="str">
@@ -5100,12 +5106,12 @@
         <v>"53": "Pero si el sacerdote ve que no se ha extendido la mancha por el vestido, tejido, cobertor o el objeto de cuero,",</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="25" t="s">
         <v>403</v>
       </c>
       <c r="C54" t="str">
@@ -5113,12 +5119,12 @@
         <v>"54": "hará lavar el objeto manchado y lo encerrará otros siete días.",</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="25" t="s">
         <v>404</v>
       </c>
       <c r="C55" t="str">
@@ -5126,12 +5132,12 @@
         <v>"55": "Si el sacerdote ve que la mancha, después de haber sido lavada, no ha mudado de aspecto, aunque la mancha no se haya extendido, el objeto es impuro; lo entregarás al fuego: es una infección por la cara y el envés.",</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="25" t="s">
         <v>405</v>
       </c>
       <c r="C56" t="str">
@@ -5139,12 +5145,12 @@
         <v>"56": "Pero si el sacerdote ve que la parte manchada, después de lavada, ha perdido color, la rasgará del vestido, del cuero, del tejido o del cobertor.",</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="25" t="s">
         <v>406</v>
       </c>
       <c r="C57" t="str">
@@ -5152,12 +5158,12 @@
         <v>"57": "Pero si vuelve a aparecer en el vestido, tejido, cobertor o en un objeto de cuero, es mal contagioso; quemarás lo que está afectado por la lepra.",</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="25" t="s">
         <v>407</v>
       </c>
       <c r="C58" t="str">
@@ -5165,12 +5171,12 @@
         <v>"58": "En cuanto al vestido, tejido, cobertor o el objeto de cuero, que después de ser lavado pierdan la mancha, serán lavados por segunda vez y quedarán puros.",</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="25" t="s">
         <v>408</v>
       </c>
       <c r="C59" t="str">
@@ -5178,7 +5184,7 @@
         <v>"59": "Estas es la ley para la mancha de lepra que se halla en los vestidos de lana o de lino, en el tejido e en el cobertor o en cualquier objeto hecho de cuero, para declararlos puros o impuros.",</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5188,7 +5194,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5198,7 +5204,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5208,7 +5214,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5218,7 +5224,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5228,7 +5234,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5238,7 +5244,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5248,7 +5254,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A130" si="3">IF(B67="","",A66+1)</f>
         <v/>
@@ -5258,7 +5264,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5268,7 +5274,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5278,7 +5284,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5288,7 +5294,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5298,7 +5304,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5308,7 +5314,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5318,7 +5324,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5328,7 +5334,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5338,7 +5344,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5348,7 +5354,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5358,7 +5364,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5368,7 +5374,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5378,7 +5384,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5388,7 +5394,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5398,7 +5404,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5408,7 +5414,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5418,7 +5424,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5428,7 +5434,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5438,7 +5444,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5448,7 +5454,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5458,7 +5464,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5468,7 +5474,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5478,7 +5484,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5488,7 +5494,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5498,7 +5504,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5508,7 +5514,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5518,7 +5524,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5528,7 +5534,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5538,7 +5544,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5548,7 +5554,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5558,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5568,7 +5574,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5578,7 +5584,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5588,7 +5594,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5598,7 +5604,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5608,7 +5614,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5618,7 +5624,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5628,7 +5634,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5638,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5648,7 +5654,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5658,7 +5664,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5668,7 +5674,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5678,7 +5684,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5688,7 +5694,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5698,7 +5704,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5708,7 +5714,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5718,7 +5724,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5728,7 +5734,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5738,7 +5744,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5748,7 +5754,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5758,7 +5764,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5768,7 +5774,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5778,7 +5784,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5788,7 +5794,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5798,7 +5804,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5808,7 +5814,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5818,7 +5824,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5828,7 +5834,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5838,7 +5844,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5848,7 +5854,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5858,7 +5864,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5868,7 +5874,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5878,7 +5884,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -5888,7 +5894,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="str">
         <f t="shared" ref="A131:A150" si="5">IF(B131="","",A130+1)</f>
         <v/>
@@ -5898,7 +5904,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5908,7 +5914,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5918,7 +5924,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5928,7 +5934,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5938,7 +5944,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5948,7 +5954,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5958,7 +5964,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5968,7 +5974,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5978,7 +5984,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5988,7 +5994,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5998,7 +6004,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6008,7 +6014,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6018,7 +6024,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6028,7 +6034,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6038,7 +6044,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6048,7 +6054,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6058,7 +6064,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6068,7 +6074,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6078,7 +6084,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6098,13 +6104,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E80DA0A-D889-4AD7-8E72-354CCA0BD24B}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B624"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="21.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="67.26953125" style="10" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="10"/>
+    <col min="1" max="2" width="67.28515625" style="10" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" s="11" customFormat="1" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>56</v>
       </c>
@@ -6112,107 +6118,107 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="13"/>
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="13"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="13"/>
       <c r="B4" s="12"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="13"/>
       <c r="B5" s="12"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="13"/>
       <c r="B6" s="12"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="13"/>
       <c r="B7" s="12"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="13"/>
       <c r="B8" s="12"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="13"/>
       <c r="B9" s="12"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="13"/>
       <c r="B10" s="12"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="13"/>
       <c r="B11" s="12"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="13"/>
       <c r="B12" s="12"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="13"/>
       <c r="B13" s="12"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="13"/>
       <c r="B14" s="12"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="13"/>
       <c r="B15" s="12"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="13"/>
       <c r="B16" s="12"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="13"/>
       <c r="B17" s="12"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="13"/>
       <c r="B18" s="12"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="13"/>
       <c r="B19" s="12"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="13"/>
       <c r="B20" s="12"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="13"/>
       <c r="B21" s="12"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="13"/>
       <c r="B22" s="12"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="13"/>
       <c r="B23" s="12"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="13"/>
       <c r="B24" s="12"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="13"/>
       <c r="B25" s="12"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="13"/>
       <c r="B26" s="12"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:2" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A27" s="10" t="s">
         <v>58</v>
       </c>
@@ -6220,107 +6226,107 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="13"/>
       <c r="B28" s="12"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="13"/>
       <c r="B29" s="12"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="13"/>
       <c r="B30" s="12"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="13"/>
       <c r="B31" s="12"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="13"/>
       <c r="B32" s="12"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="13"/>
       <c r="B33" s="12"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" s="13"/>
       <c r="B34" s="12"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" s="13"/>
       <c r="B35" s="12"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" s="13"/>
       <c r="B36" s="12"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" s="13"/>
       <c r="B37" s="12"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" s="13"/>
       <c r="B38" s="12"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" s="13"/>
       <c r="B39" s="12"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" s="13"/>
       <c r="B40" s="12"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" s="13"/>
       <c r="B41" s="12"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" s="13"/>
       <c r="B42" s="12"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" s="13"/>
       <c r="B43" s="12"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" s="13"/>
       <c r="B44" s="12"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" s="13"/>
       <c r="B45" s="12"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" s="13"/>
       <c r="B46" s="12"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" s="13"/>
       <c r="B47" s="12"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" s="13"/>
       <c r="B48" s="12"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" s="13"/>
       <c r="B49" s="12"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" s="13"/>
       <c r="B50" s="12"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" s="13"/>
       <c r="B51" s="12"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="13"/>
       <c r="B52" s="12"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" s="10" t="s">
         <v>60</v>
       </c>
@@ -6328,107 +6334,107 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" s="13"/>
       <c r="B54" s="12"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" s="13"/>
       <c r="B55" s="12"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" s="13"/>
       <c r="B56" s="12"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" s="13"/>
       <c r="B57" s="12"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" s="13"/>
       <c r="B58" s="12"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" s="13"/>
       <c r="B59" s="12"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" s="13"/>
       <c r="B60" s="12"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" s="13"/>
       <c r="B61" s="12"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" s="13"/>
       <c r="B62" s="12"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" s="13"/>
       <c r="B63" s="12"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" s="13"/>
       <c r="B64" s="12"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" s="13"/>
       <c r="B65" s="12"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" s="13"/>
       <c r="B66" s="12"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" s="13"/>
       <c r="B67" s="12"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" s="13"/>
       <c r="B68" s="12"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" s="13"/>
       <c r="B69" s="12"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" s="13"/>
       <c r="B70" s="12"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" s="13"/>
       <c r="B71" s="12"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" s="13"/>
       <c r="B72" s="12"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" s="13"/>
       <c r="B73" s="12"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" s="13"/>
       <c r="B74" s="12"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" s="13"/>
       <c r="B75" s="12"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" s="13"/>
       <c r="B76" s="12"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" s="13"/>
       <c r="B77" s="12"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" s="13"/>
       <c r="B78" s="12"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" s="10" t="s">
         <v>62</v>
       </c>
@@ -6436,107 +6442,107 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" s="13"/>
       <c r="B80" s="12"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" s="13"/>
       <c r="B81" s="12"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" s="13"/>
       <c r="B82" s="12"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" s="13"/>
       <c r="B83" s="12"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" s="13"/>
       <c r="B84" s="12"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" s="13"/>
       <c r="B85" s="12"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" s="13"/>
       <c r="B86" s="12"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" s="13"/>
       <c r="B87" s="12"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" s="13"/>
       <c r="B88" s="12"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" s="13"/>
       <c r="B89" s="12"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" s="13"/>
       <c r="B90" s="12"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" s="13"/>
       <c r="B91" s="12"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" s="13"/>
       <c r="B92" s="12"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" s="13"/>
       <c r="B93" s="12"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" s="13"/>
       <c r="B94" s="12"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" s="13"/>
       <c r="B95" s="12"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" s="13"/>
       <c r="B96" s="12"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="13"/>
       <c r="B97" s="12"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="13"/>
       <c r="B98" s="12"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="13"/>
       <c r="B99" s="12"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" s="13"/>
       <c r="B100" s="12"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" s="13"/>
       <c r="B101" s="12"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" s="13"/>
       <c r="B102" s="12"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" s="13"/>
       <c r="B103" s="12"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" s="13"/>
       <c r="B104" s="12"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" s="10" t="s">
         <v>64</v>
       </c>
@@ -6544,107 +6550,107 @@
         <v>65</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" s="13"/>
       <c r="B106" s="12"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" s="13"/>
       <c r="B107" s="12"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" s="13"/>
       <c r="B108" s="12"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" s="13"/>
       <c r="B109" s="12"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" s="13"/>
       <c r="B110" s="12"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" s="13"/>
       <c r="B111" s="12"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" s="13"/>
       <c r="B112" s="12"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" s="13"/>
       <c r="B113" s="12"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" s="13"/>
       <c r="B114" s="12"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" s="13"/>
       <c r="B115" s="12"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" s="13"/>
       <c r="B116" s="12"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" s="13"/>
       <c r="B117" s="12"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" s="13"/>
       <c r="B118" s="12"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" s="13"/>
       <c r="B119" s="12"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" s="13"/>
       <c r="B120" s="12"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" s="13"/>
       <c r="B121" s="12"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" s="13"/>
       <c r="B122" s="12"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" s="13"/>
       <c r="B123" s="12"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" s="13"/>
       <c r="B124" s="12"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" s="13"/>
       <c r="B125" s="12"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" s="13"/>
       <c r="B126" s="12"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" s="13"/>
       <c r="B127" s="12"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" s="13"/>
       <c r="B128" s="12"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" s="13"/>
       <c r="B129" s="12"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" s="13"/>
       <c r="B130" s="12"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" s="10" t="s">
         <v>66</v>
       </c>
@@ -6652,107 +6658,107 @@
         <v>67</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" s="13"/>
       <c r="B132" s="12"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" s="13"/>
       <c r="B133" s="12"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" s="13"/>
       <c r="B134" s="12"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" s="13"/>
       <c r="B135" s="12"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" s="13"/>
       <c r="B136" s="12"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" s="13"/>
       <c r="B137" s="12"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" s="13"/>
       <c r="B138" s="12"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" s="13"/>
       <c r="B139" s="12"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" s="13"/>
       <c r="B140" s="12"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" s="13"/>
       <c r="B141" s="12"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" s="13"/>
       <c r="B142" s="12"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" s="13"/>
       <c r="B143" s="12"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" s="13"/>
       <c r="B144" s="12"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" s="13"/>
       <c r="B145" s="12"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" s="13"/>
       <c r="B146" s="12"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" s="13"/>
       <c r="B147" s="12"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" s="13"/>
       <c r="B148" s="12"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" s="13"/>
       <c r="B149" s="12"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" s="13"/>
       <c r="B150" s="12"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" s="13"/>
       <c r="B151" s="12"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" s="13"/>
       <c r="B152" s="12"/>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" s="13"/>
       <c r="B153" s="12"/>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" s="13"/>
       <c r="B154" s="12"/>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" s="13"/>
       <c r="B155" s="12"/>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" s="13"/>
       <c r="B156" s="12"/>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" s="10" t="s">
         <v>68</v>
       </c>
@@ -6760,107 +6766,107 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" s="13"/>
       <c r="B158" s="12"/>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" s="13"/>
       <c r="B159" s="12"/>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" s="13"/>
       <c r="B160" s="12"/>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" s="13"/>
       <c r="B161" s="12"/>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" s="13"/>
       <c r="B162" s="12"/>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" s="13"/>
       <c r="B163" s="12"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" s="13"/>
       <c r="B164" s="12"/>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" s="13"/>
       <c r="B165" s="12"/>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" s="13"/>
       <c r="B166" s="12"/>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" s="13"/>
       <c r="B167" s="12"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" s="13"/>
       <c r="B168" s="12"/>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" s="13"/>
       <c r="B169" s="12"/>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" s="13"/>
       <c r="B170" s="12"/>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" s="13"/>
       <c r="B171" s="12"/>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" s="13"/>
       <c r="B172" s="12"/>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" s="13"/>
       <c r="B173" s="12"/>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" s="13"/>
       <c r="B174" s="12"/>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" s="13"/>
       <c r="B175" s="12"/>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" s="13"/>
       <c r="B176" s="12"/>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" s="13"/>
       <c r="B177" s="12"/>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" s="13"/>
       <c r="B178" s="12"/>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" s="13"/>
       <c r="B179" s="12"/>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" s="13"/>
       <c r="B180" s="12"/>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" s="13"/>
       <c r="B181" s="12"/>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" s="13"/>
       <c r="B182" s="12"/>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" s="10" t="s">
         <v>70</v>
       </c>
@@ -6868,107 +6874,107 @@
         <v>71</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" s="13"/>
       <c r="B184" s="12"/>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" s="13"/>
       <c r="B185" s="12"/>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" s="13"/>
       <c r="B186" s="12"/>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" s="13"/>
       <c r="B187" s="12"/>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" s="13"/>
       <c r="B188" s="12"/>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" s="13"/>
       <c r="B189" s="12"/>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" s="13"/>
       <c r="B190" s="12"/>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" s="13"/>
       <c r="B191" s="12"/>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" s="13"/>
       <c r="B192" s="12"/>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" s="13"/>
       <c r="B193" s="12"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" s="13"/>
       <c r="B194" s="12"/>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" s="13"/>
       <c r="B195" s="12"/>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" s="13"/>
       <c r="B196" s="12"/>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" s="13"/>
       <c r="B197" s="12"/>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" s="13"/>
       <c r="B198" s="12"/>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" s="13"/>
       <c r="B199" s="12"/>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" s="13"/>
       <c r="B200" s="12"/>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" s="13"/>
       <c r="B201" s="12"/>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" s="13"/>
       <c r="B202" s="12"/>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" s="13"/>
       <c r="B203" s="12"/>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" s="13"/>
       <c r="B204" s="12"/>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" s="13"/>
       <c r="B205" s="12"/>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" s="13"/>
       <c r="B206" s="12"/>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" s="13"/>
       <c r="B207" s="12"/>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" s="13"/>
       <c r="B208" s="12"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" s="10" t="s">
         <v>72</v>
       </c>
@@ -6976,107 +6982,107 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" s="13"/>
       <c r="B210" s="12"/>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" s="13"/>
       <c r="B211" s="12"/>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" s="13"/>
       <c r="B212" s="12"/>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" s="13"/>
       <c r="B213" s="12"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" s="13"/>
       <c r="B214" s="12"/>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" s="13"/>
       <c r="B215" s="12"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" s="13"/>
       <c r="B216" s="12"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" s="13"/>
       <c r="B217" s="12"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" s="13"/>
       <c r="B218" s="12"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" s="13"/>
       <c r="B219" s="12"/>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" s="13"/>
       <c r="B220" s="12"/>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" s="13"/>
       <c r="B221" s="12"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" s="13"/>
       <c r="B222" s="12"/>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" s="13"/>
       <c r="B223" s="12"/>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" s="13"/>
       <c r="B224" s="12"/>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" s="13"/>
       <c r="B225" s="12"/>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" s="13"/>
       <c r="B226" s="12"/>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" s="13"/>
       <c r="B227" s="12"/>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" s="13"/>
       <c r="B228" s="12"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" s="13"/>
       <c r="B229" s="12"/>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" s="13"/>
       <c r="B230" s="12"/>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" s="13"/>
       <c r="B231" s="12"/>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" s="13"/>
       <c r="B232" s="12"/>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" s="13"/>
       <c r="B233" s="12"/>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" s="13"/>
       <c r="B234" s="12"/>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" s="10" t="s">
         <v>74</v>
       </c>
@@ -7084,107 +7090,107 @@
         <v>75</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" s="13"/>
       <c r="B236" s="12"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" s="13"/>
       <c r="B237" s="12"/>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" s="13"/>
       <c r="B238" s="12"/>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" s="13"/>
       <c r="B239" s="12"/>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" s="13"/>
       <c r="B240" s="12"/>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" s="13"/>
       <c r="B241" s="12"/>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" s="13"/>
       <c r="B242" s="12"/>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" s="13"/>
       <c r="B243" s="12"/>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" s="13"/>
       <c r="B244" s="12"/>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" s="13"/>
       <c r="B245" s="12"/>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" s="13"/>
       <c r="B246" s="12"/>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" s="13"/>
       <c r="B247" s="12"/>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" s="13"/>
       <c r="B248" s="12"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" s="13"/>
       <c r="B249" s="12"/>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" s="13"/>
       <c r="B250" s="12"/>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" s="13"/>
       <c r="B251" s="12"/>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" s="13"/>
       <c r="B252" s="12"/>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" s="13"/>
       <c r="B253" s="12"/>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" s="13"/>
       <c r="B254" s="12"/>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" s="13"/>
       <c r="B255" s="12"/>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" s="13"/>
       <c r="B256" s="12"/>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" s="13"/>
       <c r="B257" s="12"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" s="13"/>
       <c r="B258" s="12"/>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" s="13"/>
       <c r="B259" s="12"/>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" s="13"/>
       <c r="B260" s="12"/>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" s="10" t="s">
         <v>76</v>
       </c>
@@ -7192,107 +7198,107 @@
         <v>77</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" s="13"/>
       <c r="B262" s="12"/>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" s="13"/>
       <c r="B263" s="12"/>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" s="13"/>
       <c r="B264" s="12"/>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" s="13"/>
       <c r="B265" s="12"/>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" s="13"/>
       <c r="B266" s="12"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" s="13"/>
       <c r="B267" s="12"/>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" s="13"/>
       <c r="B268" s="12"/>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" s="13"/>
       <c r="B269" s="12"/>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" s="13"/>
       <c r="B270" s="12"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" s="13"/>
       <c r="B271" s="12"/>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" s="13"/>
       <c r="B272" s="12"/>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" s="13"/>
       <c r="B273" s="12"/>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" s="13"/>
       <c r="B274" s="12"/>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" s="13"/>
       <c r="B275" s="12"/>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" s="13"/>
       <c r="B276" s="12"/>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" s="13"/>
       <c r="B277" s="12"/>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" s="13"/>
       <c r="B278" s="12"/>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" s="13"/>
       <c r="B279" s="12"/>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" s="13"/>
       <c r="B280" s="12"/>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" s="13"/>
       <c r="B281" s="12"/>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" s="13"/>
       <c r="B282" s="12"/>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" s="13"/>
       <c r="B283" s="12"/>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" s="13"/>
       <c r="B284" s="12"/>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" s="13"/>
       <c r="B285" s="12"/>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" s="13"/>
       <c r="B286" s="12"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" s="10" t="s">
         <v>78</v>
       </c>
@@ -7300,107 +7306,107 @@
         <v>79</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" s="13"/>
       <c r="B288" s="12"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" s="13"/>
       <c r="B289" s="12"/>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" s="13"/>
       <c r="B290" s="12"/>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" s="13"/>
       <c r="B291" s="12"/>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" s="13"/>
       <c r="B292" s="12"/>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" s="13"/>
       <c r="B293" s="12"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" s="13"/>
       <c r="B294" s="12"/>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" s="13"/>
       <c r="B295" s="12"/>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" s="13"/>
       <c r="B296" s="12"/>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" s="13"/>
       <c r="B297" s="12"/>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" s="13"/>
       <c r="B298" s="12"/>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" s="13"/>
       <c r="B299" s="12"/>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" s="13"/>
       <c r="B300" s="12"/>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" s="13"/>
       <c r="B301" s="12"/>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" s="13"/>
       <c r="B302" s="12"/>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" s="13"/>
       <c r="B303" s="12"/>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A304" s="13"/>
       <c r="B304" s="12"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A305" s="13"/>
       <c r="B305" s="12"/>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A306" s="13"/>
       <c r="B306" s="12"/>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A307" s="13"/>
       <c r="B307" s="12"/>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" s="13"/>
       <c r="B308" s="12"/>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A309" s="13"/>
       <c r="B309" s="12"/>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A310" s="13"/>
       <c r="B310" s="12"/>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A311" s="13"/>
       <c r="B311" s="12"/>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A312" s="13"/>
       <c r="B312" s="12"/>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A313" s="10" t="s">
         <v>80</v>
       </c>
@@ -7408,107 +7414,107 @@
         <v>81</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A314" s="13"/>
       <c r="B314" s="12"/>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A315" s="13"/>
       <c r="B315" s="12"/>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A316" s="13"/>
       <c r="B316" s="12"/>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A317" s="13"/>
       <c r="B317" s="12"/>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A318" s="13"/>
       <c r="B318" s="12"/>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A319" s="13"/>
       <c r="B319" s="12"/>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" s="13"/>
       <c r="B320" s="12"/>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A321" s="13"/>
       <c r="B321" s="12"/>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" s="13"/>
       <c r="B322" s="12"/>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A323" s="13"/>
       <c r="B323" s="12"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A324" s="13"/>
       <c r="B324" s="12"/>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" s="13"/>
       <c r="B325" s="12"/>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A326" s="13"/>
       <c r="B326" s="12"/>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A327" s="13"/>
       <c r="B327" s="12"/>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A328" s="13"/>
       <c r="B328" s="12"/>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A329" s="13"/>
       <c r="B329" s="12"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A330" s="13"/>
       <c r="B330" s="12"/>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A331" s="13"/>
       <c r="B331" s="12"/>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A332" s="13"/>
       <c r="B332" s="12"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A333" s="13"/>
       <c r="B333" s="12"/>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A334" s="13"/>
       <c r="B334" s="12"/>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A335" s="13"/>
       <c r="B335" s="12"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A336" s="13"/>
       <c r="B336" s="12"/>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A337" s="13"/>
       <c r="B337" s="12"/>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A338" s="13"/>
       <c r="B338" s="12"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A339" s="10" t="s">
         <v>82</v>
       </c>
@@ -7516,107 +7522,107 @@
         <v>83</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A340" s="13"/>
       <c r="B340" s="12"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A341" s="13"/>
       <c r="B341" s="12"/>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A342" s="13"/>
       <c r="B342" s="12"/>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A343" s="13"/>
       <c r="B343" s="12"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A344" s="13"/>
       <c r="B344" s="12"/>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A345" s="13"/>
       <c r="B345" s="12"/>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A346" s="13"/>
       <c r="B346" s="12"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A347" s="13"/>
       <c r="B347" s="12"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A348" s="13"/>
       <c r="B348" s="12"/>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A349" s="13"/>
       <c r="B349" s="12"/>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A350" s="13"/>
       <c r="B350" s="12"/>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A351" s="13"/>
       <c r="B351" s="12"/>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A352" s="13"/>
       <c r="B352" s="12"/>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A353" s="13"/>
       <c r="B353" s="12"/>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A354" s="13"/>
       <c r="B354" s="12"/>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A355" s="13"/>
       <c r="B355" s="12"/>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A356" s="13"/>
       <c r="B356" s="12"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A357" s="13"/>
       <c r="B357" s="12"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A358" s="13"/>
       <c r="B358" s="12"/>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A359" s="13"/>
       <c r="B359" s="12"/>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A360" s="13"/>
       <c r="B360" s="12"/>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A361" s="13"/>
       <c r="B361" s="12"/>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A362" s="13"/>
       <c r="B362" s="12"/>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A363" s="13"/>
       <c r="B363" s="12"/>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A364" s="13"/>
       <c r="B364" s="12"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A365" s="10" t="s">
         <v>84</v>
       </c>
@@ -7624,107 +7630,107 @@
         <v>85</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A366" s="13"/>
       <c r="B366" s="12"/>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A367" s="13"/>
       <c r="B367" s="12"/>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A368" s="13"/>
       <c r="B368" s="12"/>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A369" s="13"/>
       <c r="B369" s="12"/>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A370" s="13"/>
       <c r="B370" s="12"/>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A371" s="13"/>
       <c r="B371" s="12"/>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A372" s="13"/>
       <c r="B372" s="12"/>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A373" s="13"/>
       <c r="B373" s="12"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A374" s="13"/>
       <c r="B374" s="12"/>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A375" s="13"/>
       <c r="B375" s="12"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A376" s="13"/>
       <c r="B376" s="12"/>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A377" s="13"/>
       <c r="B377" s="12"/>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A378" s="13"/>
       <c r="B378" s="12"/>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A379" s="13"/>
       <c r="B379" s="12"/>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A380" s="13"/>
       <c r="B380" s="12"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A381" s="13"/>
       <c r="B381" s="12"/>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A382" s="13"/>
       <c r="B382" s="12"/>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A383" s="13"/>
       <c r="B383" s="12"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A384" s="13"/>
       <c r="B384" s="12"/>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A385" s="13"/>
       <c r="B385" s="12"/>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A386" s="13"/>
       <c r="B386" s="12"/>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A387" s="13"/>
       <c r="B387" s="12"/>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A388" s="13"/>
       <c r="B388" s="12"/>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A389" s="13"/>
       <c r="B389" s="12"/>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A390" s="13"/>
       <c r="B390" s="12"/>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A391" s="10" t="s">
         <v>86</v>
       </c>
@@ -7732,107 +7738,107 @@
         <v>87</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A392" s="13"/>
       <c r="B392" s="12"/>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A393" s="13"/>
       <c r="B393" s="12"/>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A394" s="13"/>
       <c r="B394" s="12"/>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A395" s="13"/>
       <c r="B395" s="12"/>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A396" s="13"/>
       <c r="B396" s="12"/>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A397" s="13"/>
       <c r="B397" s="12"/>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A398" s="13"/>
       <c r="B398" s="12"/>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A399" s="13"/>
       <c r="B399" s="12"/>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A400" s="13"/>
       <c r="B400" s="12"/>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A401" s="13"/>
       <c r="B401" s="12"/>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A402" s="13"/>
       <c r="B402" s="12"/>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A403" s="13"/>
       <c r="B403" s="12"/>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A404" s="13"/>
       <c r="B404" s="12"/>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A405" s="13"/>
       <c r="B405" s="12"/>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A406" s="13"/>
       <c r="B406" s="12"/>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A407" s="13"/>
       <c r="B407" s="12"/>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A408" s="13"/>
       <c r="B408" s="12"/>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A409" s="13"/>
       <c r="B409" s="12"/>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A410" s="13"/>
       <c r="B410" s="12"/>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A411" s="13"/>
       <c r="B411" s="12"/>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A412" s="13"/>
       <c r="B412" s="12"/>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A413" s="13"/>
       <c r="B413" s="12"/>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A414" s="13"/>
       <c r="B414" s="12"/>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A415" s="13"/>
       <c r="B415" s="12"/>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A416" s="13"/>
       <c r="B416" s="12"/>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A417" s="10" t="s">
         <v>88</v>
       </c>
@@ -7840,107 +7846,107 @@
         <v>89</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A418" s="13"/>
       <c r="B418" s="12"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A419" s="13"/>
       <c r="B419" s="12"/>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A420" s="13"/>
       <c r="B420" s="12"/>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A421" s="13"/>
       <c r="B421" s="12"/>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A422" s="13"/>
       <c r="B422" s="12"/>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A423" s="13"/>
       <c r="B423" s="12"/>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A424" s="13"/>
       <c r="B424" s="12"/>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A425" s="13"/>
       <c r="B425" s="12"/>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A426" s="13"/>
       <c r="B426" s="12"/>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A427" s="13"/>
       <c r="B427" s="12"/>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A428" s="13"/>
       <c r="B428" s="12"/>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A429" s="13"/>
       <c r="B429" s="12"/>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A430" s="13"/>
       <c r="B430" s="12"/>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A431" s="13"/>
       <c r="B431" s="12"/>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A432" s="13"/>
       <c r="B432" s="12"/>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A433" s="13"/>
       <c r="B433" s="12"/>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A434" s="13"/>
       <c r="B434" s="12"/>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A435" s="13"/>
       <c r="B435" s="12"/>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A436" s="13"/>
       <c r="B436" s="12"/>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A437" s="13"/>
       <c r="B437" s="12"/>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A438" s="13"/>
       <c r="B438" s="12"/>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A439" s="13"/>
       <c r="B439" s="12"/>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A440" s="13"/>
       <c r="B440" s="12"/>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A441" s="13"/>
       <c r="B441" s="12"/>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A442" s="13"/>
       <c r="B442" s="12"/>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A443" s="10" t="s">
         <v>90</v>
       </c>
@@ -7948,107 +7954,107 @@
         <v>91</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A444" s="13"/>
       <c r="B444" s="12"/>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A445" s="13"/>
       <c r="B445" s="12"/>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A446" s="13"/>
       <c r="B446" s="12"/>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A447" s="13"/>
       <c r="B447" s="12"/>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A448" s="13"/>
       <c r="B448" s="12"/>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A449" s="13"/>
       <c r="B449" s="12"/>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A450" s="13"/>
       <c r="B450" s="12"/>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A451" s="13"/>
       <c r="B451" s="12"/>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A452" s="13"/>
       <c r="B452" s="12"/>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A453" s="13"/>
       <c r="B453" s="12"/>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A454" s="13"/>
       <c r="B454" s="12"/>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A455" s="13"/>
       <c r="B455" s="12"/>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A456" s="13"/>
       <c r="B456" s="12"/>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A457" s="13"/>
       <c r="B457" s="12"/>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A458" s="13"/>
       <c r="B458" s="12"/>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A459" s="13"/>
       <c r="B459" s="12"/>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A460" s="13"/>
       <c r="B460" s="12"/>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A461" s="13"/>
       <c r="B461" s="12"/>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A462" s="13"/>
       <c r="B462" s="12"/>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A463" s="13"/>
       <c r="B463" s="12"/>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A464" s="13"/>
       <c r="B464" s="12"/>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A465" s="13"/>
       <c r="B465" s="12"/>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A466" s="13"/>
       <c r="B466" s="12"/>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A467" s="13"/>
       <c r="B467" s="12"/>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A468" s="13"/>
       <c r="B468" s="12"/>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A469" s="10" t="s">
         <v>92</v>
       </c>
@@ -8056,107 +8062,107 @@
         <v>93</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A470" s="13"/>
       <c r="B470" s="12"/>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A471" s="13"/>
       <c r="B471" s="12"/>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A472" s="13"/>
       <c r="B472" s="12"/>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A473" s="13"/>
       <c r="B473" s="12"/>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A474" s="13"/>
       <c r="B474" s="12"/>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A475" s="13"/>
       <c r="B475" s="12"/>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A476" s="13"/>
       <c r="B476" s="12"/>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A477" s="13"/>
       <c r="B477" s="12"/>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A478" s="13"/>
       <c r="B478" s="12"/>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A479" s="13"/>
       <c r="B479" s="12"/>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A480" s="13"/>
       <c r="B480" s="12"/>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A481" s="13"/>
       <c r="B481" s="12"/>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A482" s="13"/>
       <c r="B482" s="12"/>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A483" s="13"/>
       <c r="B483" s="12"/>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A484" s="13"/>
       <c r="B484" s="12"/>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A485" s="13"/>
       <c r="B485" s="12"/>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A486" s="13"/>
       <c r="B486" s="12"/>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A487" s="13"/>
       <c r="B487" s="12"/>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A488" s="13"/>
       <c r="B488" s="12"/>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A489" s="13"/>
       <c r="B489" s="12"/>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A490" s="13"/>
       <c r="B490" s="12"/>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A491" s="13"/>
       <c r="B491" s="12"/>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A492" s="13"/>
       <c r="B492" s="12"/>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A493" s="13"/>
       <c r="B493" s="12"/>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A494" s="13"/>
       <c r="B494" s="12"/>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A495" s="10" t="s">
         <v>94</v>
       </c>
@@ -8164,107 +8170,107 @@
         <v>95</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A496" s="13"/>
       <c r="B496" s="12"/>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A497" s="13"/>
       <c r="B497" s="12"/>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A498" s="13"/>
       <c r="B498" s="12"/>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A499" s="13"/>
       <c r="B499" s="12"/>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A500" s="13"/>
       <c r="B500" s="12"/>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A501" s="13"/>
       <c r="B501" s="12"/>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A502" s="13"/>
       <c r="B502" s="12"/>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A503" s="13"/>
       <c r="B503" s="12"/>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A504" s="13"/>
       <c r="B504" s="12"/>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A505" s="13"/>
       <c r="B505" s="12"/>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A506" s="13"/>
       <c r="B506" s="12"/>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A507" s="13"/>
       <c r="B507" s="12"/>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A508" s="13"/>
       <c r="B508" s="12"/>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A509" s="13"/>
       <c r="B509" s="12"/>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A510" s="13"/>
       <c r="B510" s="12"/>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A511" s="13"/>
       <c r="B511" s="12"/>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A512" s="13"/>
       <c r="B512" s="12"/>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A513" s="13"/>
       <c r="B513" s="12"/>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A514" s="13"/>
       <c r="B514" s="12"/>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A515" s="13"/>
       <c r="B515" s="12"/>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A516" s="13"/>
       <c r="B516" s="12"/>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A517" s="13"/>
       <c r="B517" s="12"/>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A518" s="13"/>
       <c r="B518" s="12"/>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A519" s="13"/>
       <c r="B519" s="12"/>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A520" s="13"/>
       <c r="B520" s="12"/>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A521" s="10" t="s">
         <v>96</v>
       </c>
@@ -8272,107 +8278,107 @@
         <v>97</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A522" s="13"/>
       <c r="B522" s="12"/>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A523" s="13"/>
       <c r="B523" s="12"/>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A524" s="13"/>
       <c r="B524" s="12"/>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A525" s="13"/>
       <c r="B525" s="12"/>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A526" s="13"/>
       <c r="B526" s="12"/>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A527" s="13"/>
       <c r="B527" s="12"/>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A528" s="13"/>
       <c r="B528" s="12"/>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A529" s="13"/>
       <c r="B529" s="12"/>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A530" s="13"/>
       <c r="B530" s="12"/>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A531" s="13"/>
       <c r="B531" s="12"/>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A532" s="13"/>
       <c r="B532" s="12"/>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A533" s="13"/>
       <c r="B533" s="12"/>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A534" s="13"/>
       <c r="B534" s="12"/>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A535" s="13"/>
       <c r="B535" s="12"/>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A536" s="13"/>
       <c r="B536" s="12"/>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A537" s="13"/>
       <c r="B537" s="12"/>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A538" s="13"/>
       <c r="B538" s="12"/>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A539" s="13"/>
       <c r="B539" s="12"/>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A540" s="13"/>
       <c r="B540" s="12"/>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A541" s="13"/>
       <c r="B541" s="12"/>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A542" s="13"/>
       <c r="B542" s="12"/>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A543" s="13"/>
       <c r="B543" s="12"/>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A544" s="13"/>
       <c r="B544" s="12"/>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A545" s="13"/>
       <c r="B545" s="12"/>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A546" s="13"/>
       <c r="B546" s="12"/>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A547" s="10" t="s">
         <v>98</v>
       </c>
@@ -8380,107 +8386,107 @@
         <v>99</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A548" s="13"/>
       <c r="B548" s="12"/>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A549" s="13"/>
       <c r="B549" s="12"/>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A550" s="13"/>
       <c r="B550" s="12"/>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A551" s="13"/>
       <c r="B551" s="12"/>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A552" s="13"/>
       <c r="B552" s="12"/>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A553" s="13"/>
       <c r="B553" s="12"/>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A554" s="13"/>
       <c r="B554" s="12"/>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A555" s="13"/>
       <c r="B555" s="12"/>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A556" s="13"/>
       <c r="B556" s="12"/>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A557" s="13"/>
       <c r="B557" s="12"/>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A558" s="13"/>
       <c r="B558" s="12"/>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A559" s="13"/>
       <c r="B559" s="12"/>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A560" s="13"/>
       <c r="B560" s="12"/>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A561" s="13"/>
       <c r="B561" s="12"/>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A562" s="13"/>
       <c r="B562" s="12"/>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A563" s="13"/>
       <c r="B563" s="12"/>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A564" s="13"/>
       <c r="B564" s="12"/>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A565" s="13"/>
       <c r="B565" s="12"/>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A566" s="13"/>
       <c r="B566" s="12"/>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A567" s="13"/>
       <c r="B567" s="12"/>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A568" s="13"/>
       <c r="B568" s="12"/>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A569" s="13"/>
       <c r="B569" s="12"/>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A570" s="13"/>
       <c r="B570" s="12"/>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A571" s="13"/>
       <c r="B571" s="12"/>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A572" s="13"/>
       <c r="B572" s="12"/>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A573" s="10" t="s">
         <v>100</v>
       </c>
@@ -8488,107 +8494,107 @@
         <v>101</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A574" s="13"/>
       <c r="B574" s="12"/>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A575" s="13"/>
       <c r="B575" s="12"/>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A576" s="13"/>
       <c r="B576" s="12"/>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A577" s="13"/>
       <c r="B577" s="12"/>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A578" s="13"/>
       <c r="B578" s="12"/>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A579" s="13"/>
       <c r="B579" s="12"/>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A580" s="13"/>
       <c r="B580" s="12"/>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A581" s="13"/>
       <c r="B581" s="12"/>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A582" s="13"/>
       <c r="B582" s="12"/>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A583" s="13"/>
       <c r="B583" s="12"/>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A584" s="13"/>
       <c r="B584" s="12"/>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A585" s="13"/>
       <c r="B585" s="12"/>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A586" s="13"/>
       <c r="B586" s="12"/>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A587" s="13"/>
       <c r="B587" s="12"/>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A588" s="13"/>
       <c r="B588" s="12"/>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A589" s="13"/>
       <c r="B589" s="12"/>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A590" s="13"/>
       <c r="B590" s="12"/>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A591" s="13"/>
       <c r="B591" s="12"/>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A592" s="13"/>
       <c r="B592" s="12"/>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A593" s="13"/>
       <c r="B593" s="12"/>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A594" s="13"/>
       <c r="B594" s="12"/>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A595" s="13"/>
       <c r="B595" s="12"/>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A596" s="13"/>
       <c r="B596" s="12"/>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A597" s="13"/>
       <c r="B597" s="12"/>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A598" s="13"/>
       <c r="B598" s="12"/>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A599" s="10" t="s">
         <v>102</v>
       </c>
@@ -8596,103 +8602,103 @@
         <v>103</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A600" s="13"/>
       <c r="B600" s="12"/>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A601" s="13"/>
       <c r="B601" s="12"/>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A602" s="13"/>
       <c r="B602" s="12"/>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A603" s="13"/>
       <c r="B603" s="12"/>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A604" s="13"/>
       <c r="B604" s="12"/>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A605" s="13"/>
       <c r="B605" s="12"/>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A606" s="13"/>
       <c r="B606" s="12"/>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A607" s="13"/>
       <c r="B607" s="12"/>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A608" s="13"/>
       <c r="B608" s="12"/>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A609" s="13"/>
       <c r="B609" s="12"/>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A610" s="13"/>
       <c r="B610" s="12"/>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A611" s="13"/>
       <c r="B611" s="12"/>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A612" s="13"/>
       <c r="B612" s="12"/>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A613" s="13"/>
       <c r="B613" s="12"/>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A614" s="13"/>
       <c r="B614" s="12"/>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A615" s="13"/>
       <c r="B615" s="12"/>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A616" s="13"/>
       <c r="B616" s="12"/>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A617" s="13"/>
       <c r="B617" s="12"/>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A618" s="13"/>
       <c r="B618" s="12"/>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A619" s="13"/>
       <c r="B619" s="12"/>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A620" s="13"/>
       <c r="B620" s="12"/>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A621" s="13"/>
       <c r="B621" s="12"/>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A622" s="13"/>
       <c r="B622" s="12"/>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A623" s="13"/>
       <c r="B623" s="12"/>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A624" s="13"/>
       <c r="B624" s="12"/>
     </row>
@@ -8706,7 +8712,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE1588A-237E-4EC7-ABEF-3BC1FE76A1BD}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8717,22 +8723,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E047D162-2EDF-4160-B322-2826A8095468}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:C31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.1796875" customWidth="1"/>
+    <col min="1" max="1" width="1.140625" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" customWidth="1"/>
-    <col min="4" max="4" width="1.26953125" customWidth="1"/>
-    <col min="5" max="5" width="70.7265625" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" customWidth="1"/>
+    <col min="4" max="4" width="1.28515625" customWidth="1"/>
+    <col min="5" max="5" width="70.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="25" t="s">
+    <row r="2" spans="2:3" ht="24" x14ac:dyDescent="0.4">
+      <c r="B2" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="25"/>
-    </row>
-    <row r="3" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="C2" s="30"/>
+    </row>
+    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>106</v>
       </c>
@@ -8740,7 +8746,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="17" t="s">
         <v>104</v>
       </c>
@@ -8748,11 +8754,11 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
-    <row r="6" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>111</v>
       </c>
@@ -8760,7 +8766,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="20" t="s">
         <v>107</v>
       </c>
@@ -8768,7 +8774,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B8" s="22" t="s">
         <v>104</v>
       </c>
@@ -8776,11 +8782,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
         <v>112</v>
       </c>
@@ -8788,7 +8794,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>113</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B12" s="22" t="s">
         <v>104</v>
       </c>
@@ -8804,11 +8810,11 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
     </row>
-    <row r="14" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B14" s="15" t="s">
         <v>117</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B15" s="20" t="s">
         <v>118</v>
       </c>
@@ -8824,7 +8830,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
         <v>104</v>
       </c>
@@ -8832,11 +8838,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
         <v>122</v>
       </c>
@@ -8844,7 +8850,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>121</v>
       </c>
@@ -8852,11 +8858,11 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
     </row>
-    <row r="21" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B21" s="15" t="s">
         <v>125</v>
       </c>
@@ -8864,7 +8870,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B22" s="20" t="s">
         <v>126</v>
       </c>
@@ -8872,49 +8878,49 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
-    <row r="25" spans="2:3" ht="39" x14ac:dyDescent="0.35">
-      <c r="B25" s="26" t="str">
+    <row r="25" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="str">
         <f>_xlfn.CONCAT(B7," | ",C7)</f>
         <v>1ra. Lectura | Genesis 3,1-7</v>
       </c>
-      <c r="C25" s="26"/>
-    </row>
-    <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="31"/>
+    </row>
+    <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
     </row>
-    <row r="27" spans="2:3" ht="39" x14ac:dyDescent="0.35">
-      <c r="B27" s="26" t="str">
+    <row r="27" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="str">
         <f>_xlfn.CONCAT(B11," | ",C11)</f>
         <v>2ra. Lectura | Isaías 53,6-10</v>
       </c>
-      <c r="C27" s="26"/>
-    </row>
-    <row r="28" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-    </row>
-    <row r="29" spans="2:3" ht="39" x14ac:dyDescent="0.35">
-      <c r="B29" s="26" t="str">
+      <c r="C27" s="31"/>
+    </row>
+    <row r="28" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+    </row>
+    <row r="29" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="31" t="str">
         <f>_xlfn.CONCAT(B15," | ",C15)</f>
         <v>3ra. Lectura | Filipenses 2,6-11</v>
       </c>
-      <c r="C29" s="26"/>
-    </row>
-    <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-    </row>
-    <row r="31" spans="2:3" ht="39" x14ac:dyDescent="0.35">
-      <c r="B31" s="26" t="str">
+      <c r="C29" s="31"/>
+    </row>
+    <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+    </row>
+    <row r="31" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="31" t="str">
         <f>_xlfn.CONCAT(B19," | ",C19)</f>
         <v>Evangelio | Marcos 25,12-15</v>
       </c>
-      <c r="C31" s="26"/>
+      <c r="C31" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8937,14 +8943,14 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -8958,7 +8964,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -8972,7 +8978,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -8986,7 +8992,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -9000,7 +9006,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -9028,7 +9034,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -9042,7 +9048,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -9056,7 +9062,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -9070,7 +9076,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -9084,7 +9090,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -9098,7 +9104,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -9112,7 +9118,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -9126,7 +9132,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -9140,7 +9146,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -9154,7 +9160,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -9168,7 +9174,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -9182,7 +9188,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -9196,7 +9202,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -9210,7 +9216,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -9224,7 +9230,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -9238,7 +9244,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -9252,7 +9258,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -9266,7 +9272,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -9280,7 +9286,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -9294,7 +9300,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
@@ -9308,7 +9314,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
@@ -9322,7 +9328,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
@@ -9336,7 +9342,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>29</v>
       </c>
@@ -9350,7 +9356,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
       </c>
@@ -9364,7 +9370,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>31</v>
       </c>
@@ -9378,7 +9384,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>32</v>
       </c>
@@ -9392,7 +9398,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>33</v>
       </c>
@@ -9406,7 +9412,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>34</v>
       </c>
@@ -9420,7 +9426,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>35</v>
       </c>
@@ -9434,7 +9440,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
@@ -9448,7 +9454,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>37</v>
       </c>
@@ -9462,7 +9468,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>38</v>
       </c>
@@ -9476,7 +9482,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>39</v>
       </c>
@@ -9490,7 +9496,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>40</v>
       </c>
@@ -9504,7 +9510,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>41</v>
       </c>
@@ -9518,7 +9524,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>42</v>
       </c>
@@ -9532,7 +9538,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>43</v>
       </c>
@@ -9546,7 +9552,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>44</v>
       </c>
@@ -9560,7 +9566,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>45</v>
       </c>
@@ -9574,7 +9580,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>46</v>
       </c>
@@ -9588,7 +9594,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>47</v>
       </c>
@@ -9602,7 +9608,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>48</v>
       </c>
@@ -9616,7 +9622,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>49</v>
       </c>
@@ -9630,7 +9636,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>50</v>
       </c>
@@ -9644,7 +9650,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>51</v>
       </c>
@@ -9658,7 +9664,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>52</v>
       </c>
@@ -9672,7 +9678,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>53</v>
       </c>
@@ -9686,7 +9692,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>54</v>
       </c>
@@ -9700,7 +9706,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>55</v>
       </c>
@@ -9714,7 +9720,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>56</v>
       </c>
@@ -9728,7 +9734,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>57</v>
       </c>
@@ -9742,7 +9748,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>58</v>
       </c>
@@ -9756,7 +9762,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>59</v>
       </c>
@@ -9770,7 +9776,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>60</v>
       </c>
@@ -9784,7 +9790,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>61</v>
       </c>
@@ -9798,7 +9804,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>62</v>
       </c>
@@ -9812,7 +9818,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
@@ -9826,7 +9832,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>64</v>
       </c>
@@ -9840,7 +9846,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>65</v>
       </c>
@@ -9854,7 +9860,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>66</v>
       </c>
@@ -9868,7 +9874,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>67</v>
       </c>
@@ -9882,7 +9888,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>68</v>
       </c>
@@ -9896,7 +9902,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>69</v>
       </c>
@@ -9910,7 +9916,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70</v>
       </c>
@@ -9924,7 +9930,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>71</v>
       </c>
@@ -9938,7 +9944,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>72</v>
       </c>
@@ -9952,7 +9958,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>73</v>
       </c>
@@ -9978,723 +9984,723 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C150"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="C1" s="29" t="str">
+      <c r="C1" s="27" t="str">
         <f>IF(B1="","",_xlfn.CONCAT("""",A1,"""",": """,B1,"""",","))</f>
         <v>"1": "Yahveh habló a Moisés y Aarón diciendo:",</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>IF(B2="","",A1+1)</f>
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>410</v>
       </c>
-      <c r="C2" s="29" t="str">
+      <c r="C2" s="27" t="str">
         <f t="shared" ref="C2:C65" si="0">IF(B2="","",_xlfn.CONCAT("""",A2,"""",": """,B2,"""",","))</f>
         <v>"2": "Hablad a los israelitas y decidles: Cualquier hombre que padece flujo seminal es impuro a causa del flujo.",</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" ref="A3:A66" si="1">IF(B3="","",A2+1)</f>
         <v>3</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>411</v>
       </c>
-      <c r="C3" s="29" t="str">
+      <c r="C3" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"3": "En esto consiste la impureza causada por su flujo: sea que su cuerpo deje destilar el flujo, o lo retenga, es impuro.",</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="C4" s="29" t="str">
+      <c r="C4" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"4": "Todo lecho en que duerma el que padece flujo será impuro y todo asiento en que se siente será impuro.",</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="C5" s="29" t="str">
+      <c r="C5" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"5": "Quien toque su lecho lavará sus vestidos, se bañará en agua y quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="C6" s="29" t="str">
+      <c r="C6" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"6": "Quien se siente sobre un mueble donde se haya sentado cualquiera que padece flujo lavará sus vestidos, se bañará en agua y será impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="C7" s="29" t="str">
+      <c r="C7" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"7": "Quien toque el cuerpo del que padece flujo lavará sus vestidos, se bañará en agua y será impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="25" t="s">
         <v>416</v>
       </c>
-      <c r="C8" s="29" t="str">
+      <c r="C8" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"8": "Si el que tiene flujo escupe sobre un hombre puro, éste lavará sus vestidos, se bañará en agua y quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="C9" s="29" t="str">
+      <c r="C9" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"9": "Todo aparejo sobre el cual haya montado el que padece flujo será inmundo.",</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="C10" s="29" t="str">
+      <c r="C10" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"10": "Quien toque un objeto que haya estado debajo de él quedará impuro hasta la tarde. Y el que los lleve lavará sus vestidos, se bañará en agua y será impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>419</v>
       </c>
-      <c r="C11" s="29" t="str">
+      <c r="C11" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"11": "Todo aquel a quien toque el que padece flujo sin haberse lavado las manos con agua lavará sus vestidos, se bañará en agua y quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="25" t="s">
         <v>420</v>
       </c>
-      <c r="C12" s="29" t="str">
+      <c r="C12" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"12": "Toda vasija de barro tocada por el que padece flujo será rota, y todo utensilio de madera será lavado con agua.",</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="C13" s="29" t="str">
+      <c r="C13" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"13": "Si el que padece flujo sana de él, se contarán siete días para su purificaión; después lavará sus vestidos, se bañará en agua viva y quedará puro.",</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="25" t="s">
         <v>422</v>
       </c>
-      <c r="C14" s="29" t="str">
+      <c r="C14" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"14": "Al día octavo tomará dos tórtolas o dos pichones y se presentará ante Yahveh a la entrada de la Tienda del Encuentro, para entregarlos al sacerdote.",</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="25" t="s">
         <v>423</v>
       </c>
-      <c r="C15" s="29" t="str">
+      <c r="C15" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"15": "El sacerdote los ofrecerá, uno como sacrificio por el pecado, el otro como holocausto, y de esta manera el sacerdote hará expiación por él ante Yahveh, a causa de su flujo.",</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="C16" s="29" t="str">
+      <c r="C16" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"16": "El hombre que tenga derrame seminal lavará con agua todo su cuerpo y quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="C17" s="29" t="str">
+      <c r="C17" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"17": "Toda ropa y todo cuero sobre los cuales se haya derramado el semen serán lavados con agua y quedarán impuros hasta la tarde.",</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="25" t="s">
         <v>426</v>
       </c>
-      <c r="C18" s="29" t="str">
+      <c r="C18" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"18": "Cuando una mujer se acueste con un hombre, produciéndose efusión de semen, se bañarán ambos con agua y quedarán impuros hasta la tarde.",</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="25" t="s">
         <v>427</v>
       </c>
-      <c r="C19" s="29" t="str">
+      <c r="C19" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"19": "La mujer que tiene flujo, el flujo de sangre de su cuerpo, permanecerá en su impureza por espacio de siete días. Y quien la toque será impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="25" t="s">
         <v>428</v>
       </c>
-      <c r="C20" s="29" t="str">
+      <c r="C20" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"20": "Todo aquello sobre lo que se acueste durante su impureza quedará impuro; y todo aquello sobre lo que se siente quedará impuro.",</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>429</v>
       </c>
-      <c r="C21" s="29" t="str">
+      <c r="C21" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"21": "Quien toque su lecho lavará los vestidos, se bañará en agua y permanecerá impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="25" t="s">
         <v>430</v>
       </c>
-      <c r="C22" s="29" t="str">
+      <c r="C22" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"22": "Quien toque un mueble cualquiera sobre el que ella se haya sentado lavará sus vestidos, se bañará en agua y será impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="25" t="s">
         <v>431</v>
       </c>
-      <c r="C23" s="29" t="str">
+      <c r="C23" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"23": "Quien toque algo que esté puesto sobre el lecho o sobre el mueble donde ella se sienta quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="25" t="s">
         <v>432</v>
       </c>
-      <c r="C24" s="29" t="str">
+      <c r="C24" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"24": "Si uno se acuesta con ella se contamina de la impureza de sus reglas y queda impuro siete días; todo lecho en que él se acueste será impuro.",</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="C25" s="29" t="str">
+      <c r="C25" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"25": "Cuando una mujer tenga flujo de sangre durante muchos días, fuera del tiempo de sus reglas o cuando sus reglas se prolonguen, quedará impura mientras dure el flujo de su impureza como en los días del flujo menstrual.",</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="25" t="s">
         <v>434</v>
       </c>
-      <c r="C26" s="29" t="str">
+      <c r="C26" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"26": "Todo lecho en que se acueste mientras dura su flujo será impuro como el lecho de la menstruación, y cualquier mueble sobre el que se siente quedará impuro como en la impureza de las reglas.",</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="29" t="str">
+      <c r="C27" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"27": "Quien los toque quedará impuro y lavará sus vestidos, se bañará en agua u quedará impuro hasta la tarde.",</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="29" t="str">
+      <c r="C28" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"28": "Una vez que ella sane de su flujo, contará siete días, quedando después pura.",</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="25" t="s">
         <v>437</v>
       </c>
-      <c r="C29" s="29" t="str">
+      <c r="C29" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"29": "Al octavo día tomará para sí dos tórtolas o dos pichones y los presentará al sacerdote a la entrada de la Tienda del Encuentro.",</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="25" t="s">
         <v>438</v>
       </c>
-      <c r="C30" s="29" t="str">
+      <c r="C30" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"30": "El sacerdote los ofrecerá uno como sacrificio por el pecado, el otro como holocausto; y hará expiación por ella ante Yahveh por la impureza de su flujo.",</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="25" t="s">
         <v>439</v>
       </c>
-      <c r="C31" s="29" t="str">
+      <c r="C31" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"31": "Mantendréis alejados a los israelitas de sus impurezas para que no mueran a causa de ellas por contaminar mi Morada, la que está en medio de ellos.",</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="25" t="s">
         <v>440</v>
       </c>
-      <c r="C32" s="29" t="str">
+      <c r="C32" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"32": "Esta es la ley relativa al hombre que padece flujo o que se hace impuro con efusión de semen,",</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="25" t="s">
         <v>441</v>
       </c>
-      <c r="C33" s="29" t="str">
+      <c r="C33" s="27" t="str">
         <f t="shared" si="0"/>
         <v>"33": "a la indispuesta por el flujo menstrual, a aquel que padece flujo, sea varón o mujer, y a aquel que se acueste con una mujer en período de impureza.",</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="29" t="str">
+      <c r="B34" s="25"/>
+      <c r="C34" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="29" t="str">
+      <c r="B35" s="25"/>
+      <c r="C35" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="29" t="str">
+      <c r="B36" s="25"/>
+      <c r="C36" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="29" t="str">
+      <c r="B37" s="25"/>
+      <c r="C37" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="29" t="str">
+      <c r="B38" s="25"/>
+      <c r="C38" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="29" t="str">
+      <c r="B39" s="25"/>
+      <c r="C39" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="29" t="str">
+      <c r="B40" s="25"/>
+      <c r="C40" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="29" t="str">
+      <c r="B41" s="25"/>
+      <c r="C41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="29" t="str">
+      <c r="B42" s="25"/>
+      <c r="C42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="29" t="str">
+      <c r="B43" s="25"/>
+      <c r="C43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="29" t="str">
+      <c r="B44" s="25"/>
+      <c r="C44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="29" t="str">
+      <c r="B45" s="25"/>
+      <c r="C45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="29" t="str">
+      <c r="B46" s="25"/>
+      <c r="C46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="29" t="str">
+      <c r="B47" s="25"/>
+      <c r="C47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="29" t="str">
+      <c r="B48" s="25"/>
+      <c r="C48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="29" t="str">
+      <c r="B49" s="25"/>
+      <c r="C49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="29" t="str">
+      <c r="B50" s="25"/>
+      <c r="C50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="29" t="str">
+      <c r="B51" s="25"/>
+      <c r="C51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="29" t="str">
+      <c r="B52" s="25"/>
+      <c r="C52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B53" s="27"/>
-      <c r="C53" s="29" t="str">
+      <c r="B53" s="25"/>
+      <c r="C53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="29" t="str">
+      <c r="B54" s="25"/>
+      <c r="C54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29" t="str">
+      <c r="B55" s="25"/>
+      <c r="C55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B56" s="27"/>
-      <c r="C56" s="29" t="str">
+      <c r="B56" s="25"/>
+      <c r="C56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29" t="str">
+      <c r="B57" s="25"/>
+      <c r="C57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B58" s="27"/>
+      <c r="B58" s="25"/>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="B59" s="27"/>
+      <c r="B59" s="25"/>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10704,7 +10710,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10714,7 +10720,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10724,7 +10730,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10734,7 +10740,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10744,7 +10750,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10754,7 +10760,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10764,7 +10770,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A130" si="3">IF(B67="","",A66+1)</f>
         <v/>
@@ -10774,7 +10780,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10784,7 +10790,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10794,7 +10800,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10804,7 +10810,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10814,7 +10820,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10824,7 +10830,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10834,7 +10840,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10844,7 +10850,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10854,7 +10860,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10864,7 +10870,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10874,7 +10880,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10884,7 +10890,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10894,7 +10900,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10904,7 +10910,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10914,7 +10920,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10924,7 +10930,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10934,7 +10940,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10944,7 +10950,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10954,7 +10960,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10964,7 +10970,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10974,7 +10980,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10984,7 +10990,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -10994,7 +11000,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11004,7 +11010,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11014,7 +11020,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11024,7 +11030,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11034,7 +11040,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11044,7 +11050,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11054,7 +11060,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11064,7 +11070,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11074,7 +11080,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11084,7 +11090,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11094,7 +11100,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11104,7 +11110,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11114,7 +11120,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11124,7 +11130,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11134,7 +11140,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11144,7 +11150,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11154,7 +11160,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11164,7 +11170,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11174,7 +11180,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11184,7 +11190,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11194,7 +11200,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11204,7 +11210,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11214,7 +11220,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11224,7 +11230,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11234,7 +11240,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11244,7 +11250,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11254,7 +11260,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11264,7 +11270,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11274,7 +11280,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11284,7 +11290,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11294,7 +11300,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11304,7 +11310,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11314,7 +11320,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11324,7 +11330,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11334,7 +11340,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11344,7 +11350,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11354,7 +11360,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11364,7 +11370,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11374,7 +11380,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11384,7 +11390,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11394,7 +11400,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11404,7 +11410,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="str">
         <f t="shared" ref="A131:A150" si="5">IF(B131="","",A130+1)</f>
         <v/>
@@ -11414,7 +11420,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11424,7 +11430,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11434,7 +11440,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11444,7 +11450,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11454,7 +11460,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11464,7 +11470,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11474,7 +11480,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11484,7 +11490,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11494,7 +11500,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11504,7 +11510,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11514,7 +11520,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11524,7 +11530,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11534,7 +11540,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11544,7 +11550,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11554,7 +11560,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11564,7 +11570,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11574,7 +11580,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11584,7 +11590,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11594,7 +11600,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11614,19 +11620,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE78A61-B89A-4E11-A893-87E9D739AD96}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C90"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" customWidth="1"/>
-    <col min="2" max="2" width="40.6328125" customWidth="1"/>
-    <col min="3" max="3" width="188.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="188.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30"/>
-      <c r="B1" s="30"/>
-    </row>
-    <row r="2" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>442</v>
       </c>
       <c r="B2" t="s">
@@ -11636,8 +11642,8 @@
         <v>512</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>443</v>
       </c>
       <c r="B3" t="s">
@@ -11647,8 +11653,8 @@
         <v>514</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
         <v>444</v>
       </c>
       <c r="B4" t="s">
@@ -11658,8 +11664,8 @@
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>445</v>
       </c>
       <c r="B5" t="s">
@@ -11669,8 +11675,8 @@
         <v>518</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>446</v>
       </c>
       <c r="B6" t="s">
@@ -11680,8 +11686,8 @@
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>447</v>
       </c>
       <c r="B7" t="s">
@@ -11691,8 +11697,8 @@
         <v>522</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>448</v>
       </c>
       <c r="B8" t="s">
@@ -11702,8 +11708,8 @@
         <v>524</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
         <v>449</v>
       </c>
       <c r="B9" t="s">
@@ -11713,8 +11719,8 @@
         <v>526</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
         <v>450</v>
       </c>
       <c r="B10" t="s">
@@ -11724,8 +11730,8 @@
         <v>528</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>451</v>
       </c>
       <c r="B11" t="s">
@@ -11735,8 +11741,8 @@
         <v>530</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
         <v>452</v>
       </c>
       <c r="B12" t="s">
@@ -11746,8 +11752,8 @@
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>453</v>
       </c>
       <c r="B13" t="s">
@@ -11757,8 +11763,8 @@
         <v>534</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
         <v>454</v>
       </c>
       <c r="B14" t="s">
@@ -11768,8 +11774,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
         <v>455</v>
       </c>
       <c r="B15" t="s">
@@ -11779,8 +11785,8 @@
         <v>538</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>456</v>
       </c>
       <c r="B16" t="s">
@@ -11790,8 +11796,8 @@
         <v>540</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
         <v>457</v>
       </c>
       <c r="B17" t="s">
@@ -11801,8 +11807,8 @@
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
         <v>458</v>
       </c>
       <c r="B18" t="s">
@@ -11812,8 +11818,8 @@
         <v>544</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>459</v>
       </c>
       <c r="B19" t="s">
@@ -11823,8 +11829,8 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="31" t="s">
+    <row r="20" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>460</v>
       </c>
       <c r="B20" t="s">
@@ -11834,8 +11840,8 @@
         <v>548</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="31" t="s">
+    <row r="21" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>461</v>
       </c>
       <c r="B21" t="s">
@@ -11845,8 +11851,8 @@
         <v>550</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="31" t="s">
+    <row r="22" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
         <v>462</v>
       </c>
       <c r="B22" t="s">
@@ -11856,8 +11862,8 @@
         <v>552</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>463</v>
       </c>
       <c r="B23" t="s">
@@ -11867,8 +11873,8 @@
         <v>554</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
+    <row r="24" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
         <v>464</v>
       </c>
       <c r="B24" t="s">
@@ -11878,8 +11884,8 @@
         <v>556</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="31" t="s">
+    <row r="25" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
         <v>465</v>
       </c>
       <c r="B25" t="s">
@@ -11889,8 +11895,8 @@
         <v>558</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="29" t="s">
         <v>466</v>
       </c>
       <c r="B26" t="s">
@@ -11900,8 +11906,8 @@
         <v>560</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="29" t="s">
         <v>467</v>
       </c>
       <c r="B27" t="s">
@@ -11911,8 +11917,8 @@
         <v>562</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="31" t="s">
+    <row r="28" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="29" t="s">
         <v>468</v>
       </c>
       <c r="B28" t="s">
@@ -11922,8 +11928,8 @@
         <v>564</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="31" t="s">
+    <row r="29" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>469</v>
       </c>
       <c r="B29" t="s">
@@ -11933,8 +11939,8 @@
         <v>566</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="31" t="s">
+    <row r="30" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
         <v>470</v>
       </c>
       <c r="B30" t="s">
@@ -11944,8 +11950,8 @@
         <v>568</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="29" t="s">
         <v>471</v>
       </c>
       <c r="B31" t="s">
@@ -11955,8 +11961,8 @@
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="31" t="s">
+    <row r="32" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="29" t="s">
         <v>472</v>
       </c>
       <c r="B32" t="s">
@@ -11966,8 +11972,8 @@
         <v>572</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
         <v>473</v>
       </c>
       <c r="B33" t="s">
@@ -11977,8 +11983,8 @@
         <v>574</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="31" t="s">
+    <row r="34" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>474</v>
       </c>
       <c r="B34" t="s">
@@ -11988,8 +11994,8 @@
         <v>576</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="31" t="s">
+    <row r="35" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
         <v>475</v>
       </c>
       <c r="B35" t="s">
@@ -11999,8 +12005,8 @@
         <v>578</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="31" t="s">
+    <row r="36" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="29" t="s">
         <v>476</v>
       </c>
       <c r="B36" t="s">
@@ -12010,8 +12016,8 @@
         <v>580</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="31" t="s">
+    <row r="37" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="29" t="s">
         <v>477</v>
       </c>
       <c r="B37" t="s">
@@ -12021,8 +12027,8 @@
         <v>582</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
         <v>478</v>
       </c>
       <c r="B38" t="s">
@@ -12032,8 +12038,8 @@
         <v>584</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="31" t="s">
+    <row r="39" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
         <v>479</v>
       </c>
       <c r="B39" t="s">
@@ -12043,8 +12049,8 @@
         <v>586</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="31" t="s">
+    <row r="40" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
         <v>480</v>
       </c>
       <c r="B40" t="s">
@@ -12054,8 +12060,8 @@
         <v>588</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="31" t="s">
+    <row r="41" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="29" t="s">
         <v>481</v>
       </c>
       <c r="B41" t="s">
@@ -12065,8 +12071,8 @@
         <v>590</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="31" t="s">
+    <row r="42" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
         <v>482</v>
       </c>
       <c r="B42" t="s">
@@ -12076,8 +12082,8 @@
         <v>592</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="31" t="s">
+    <row r="43" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="29" t="s">
         <v>483</v>
       </c>
       <c r="B43" t="s">
@@ -12087,8 +12093,8 @@
         <v>594</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="31" t="s">
+    <row r="44" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>484</v>
       </c>
       <c r="B44" t="s">
@@ -12098,8 +12104,8 @@
         <v>596</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="29" t="s">
         <v>485</v>
       </c>
       <c r="B45" t="s">
@@ -12109,8 +12115,8 @@
         <v>598</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="31" t="s">
+    <row r="46" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="29" t="s">
         <v>486</v>
       </c>
       <c r="B46" t="s">
@@ -12120,8 +12126,8 @@
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="31" t="s">
+    <row r="47" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
         <v>487</v>
       </c>
       <c r="B47" t="s">
@@ -12131,8 +12137,8 @@
         <v>602</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="31" t="s">
+    <row r="48" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="29" t="s">
         <v>488</v>
       </c>
       <c r="B48" t="s">
@@ -12142,8 +12148,8 @@
         <v>604</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="31" t="s">
+    <row r="49" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
         <v>489</v>
       </c>
       <c r="B49" t="s">
@@ -12153,8 +12159,8 @@
         <v>606</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="31" t="s">
+    <row r="50" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
         <v>490</v>
       </c>
       <c r="B50" t="s">
@@ -12164,8 +12170,8 @@
         <v>608</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="31" t="s">
+    <row r="51" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="29" t="s">
         <v>491</v>
       </c>
       <c r="B51" t="s">
@@ -12175,8 +12181,8 @@
         <v>610</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="31" t="s">
+    <row r="52" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="29" t="s">
         <v>492</v>
       </c>
       <c r="B52" t="s">
@@ -12186,8 +12192,8 @@
         <v>612</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="31" t="s">
+    <row r="53" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="29" t="s">
         <v>493</v>
       </c>
       <c r="B53" t="s">
@@ -12197,8 +12203,8 @@
         <v>614</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A54" s="29" t="s">
         <v>494</v>
       </c>
       <c r="B54" t="s">
@@ -12208,8 +12214,8 @@
         <v>616</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="31" t="s">
+    <row r="55" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A55" s="29" t="s">
         <v>495</v>
       </c>
       <c r="B55" t="s">
@@ -12219,8 +12225,8 @@
         <v>618</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="31" t="s">
+    <row r="56" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="29" t="s">
         <v>496</v>
       </c>
       <c r="B56" t="s">
@@ -12230,8 +12236,8 @@
         <v>620</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="31" t="s">
+    <row r="57" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="29" t="s">
         <v>497</v>
       </c>
       <c r="B57" t="s">
@@ -12241,8 +12247,8 @@
         <v>622</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="31" t="s">
+    <row r="58" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="29" t="s">
         <v>498</v>
       </c>
       <c r="B58" t="s">
@@ -12252,8 +12258,8 @@
         <v>624</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="31" t="s">
+    <row r="59" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
         <v>499</v>
       </c>
       <c r="B59" t="s">
@@ -12263,8 +12269,8 @@
         <v>626</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="31" t="s">
+    <row r="60" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="29" t="s">
         <v>500</v>
       </c>
       <c r="B60" t="s">
@@ -12274,8 +12280,8 @@
         <v>628</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="31" t="s">
+    <row r="61" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A61" s="29" t="s">
         <v>501</v>
       </c>
       <c r="B61" t="s">
@@ -12285,8 +12291,8 @@
         <v>630</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="31" t="s">
+    <row r="62" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="29" t="s">
         <v>502</v>
       </c>
       <c r="B62" t="s">
@@ -12296,8 +12302,8 @@
         <v>632</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="31" t="s">
+    <row r="63" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
         <v>503</v>
       </c>
       <c r="B63" t="s">
@@ -12307,8 +12313,8 @@
         <v>634</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="31" t="s">
+    <row r="64" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="29" t="s">
         <v>504</v>
       </c>
       <c r="B64" t="s">
@@ -12318,8 +12324,8 @@
         <v>636</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A65" s="31" t="s">
+    <row r="65" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="29" t="s">
         <v>505</v>
       </c>
       <c r="B65" t="s">
@@ -12329,8 +12335,8 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="31" t="s">
+    <row r="66" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
         <v>506</v>
       </c>
       <c r="B66" t="s">
@@ -12340,8 +12346,8 @@
         <v>640</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="31" t="s">
+    <row r="67" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
         <v>507</v>
       </c>
       <c r="B67" t="s">
@@ -12351,8 +12357,8 @@
         <v>642</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="31" t="s">
+    <row r="68" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
         <v>508</v>
       </c>
       <c r="B68" t="s">
@@ -12362,8 +12368,8 @@
         <v>644</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="31" t="s">
+    <row r="69" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
         <v>509</v>
       </c>
       <c r="B69" t="s">
@@ -12373,8 +12379,8 @@
         <v>646</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="31" t="s">
+    <row r="70" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="29" t="s">
         <v>510</v>
       </c>
       <c r="B70" t="s">
@@ -12384,65 +12390,65 @@
         <v>648</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="28"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="28"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="28"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="28"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="28"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="28"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="28"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="28"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="28"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="28"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="28"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="28"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="28"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" s="28"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="28"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="28"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="28"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="28"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="28"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="28"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="26"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="26"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="26"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="26"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="26"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="26"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="26"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="26"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="26"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="26"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="26"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="26"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="26"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="26"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="26"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="26"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="26"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="26"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="26"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12459,13 +12465,13 @@
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
-                    <xdr:colOff>1149350</xdr:colOff>
+                    <xdr:colOff>1152525</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>50800</xdr:rowOff>
+                    <xdr:rowOff>47625</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>1193800</xdr:colOff>
+                    <xdr:colOff>1190625</xdr:colOff>
                     <xdr:row>0</xdr:row>
                     <xdr:rowOff>209550</xdr:rowOff>
                   </to>
@@ -12481,15 +12487,15 @@
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>1339850</xdr:colOff>
+                    <xdr:colOff>1343025</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>44450</xdr:rowOff>
+                    <xdr:rowOff>47625</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>2292350</xdr:colOff>
+                    <xdr:colOff>2295525</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>203200</xdr:rowOff>
+                    <xdr:rowOff>200025</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>

--- a/book/src/doc/Libros.xlsx
+++ b/book/src/doc/Libros.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F398F80F-437D-4FDF-BEEF-88617B7BAC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="7" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="5" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11622,17 +11622,17 @@
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16722,10 +16722,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="28"/>
+      <c r="C2" s="30"/>
     </row>
     <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
@@ -16872,44 +16872,44 @@
       <c r="C23" s="14"/>
     </row>
     <row r="25" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="str">
+      <c r="B25" s="31" t="str">
         <f>_xlfn.CONCAT(B7," | ",C7)</f>
         <v>1ra. Lectura | Genesis 3,1-7</v>
       </c>
-      <c r="C25" s="29"/>
+      <c r="C25" s="31"/>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
     </row>
     <row r="27" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="str">
+      <c r="B27" s="31" t="str">
         <f>_xlfn.CONCAT(B11," | ",C11)</f>
         <v>2ra. Lectura | Isaías 53,6-10</v>
       </c>
-      <c r="C27" s="29"/>
+      <c r="C27" s="31"/>
     </row>
     <row r="28" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
     </row>
     <row r="29" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="29" t="str">
+      <c r="B29" s="31" t="str">
         <f>_xlfn.CONCAT(B15," | ",C15)</f>
         <v>3ra. Lectura | Filipenses 2,6-11</v>
       </c>
-      <c r="C29" s="29"/>
+      <c r="C29" s="31"/>
     </row>
     <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
     </row>
     <row r="31" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="29" t="str">
+      <c r="B31" s="31" t="str">
         <f>_xlfn.CONCAT(B19," | ",C19)</f>
         <v>Evangelio | Marcos 25,12-15</v>
       </c>
-      <c r="C31" s="29"/>
+      <c r="C31" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -19621,7 +19621,7 @@
       <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>442</v>
       </c>
       <c r="B2" t="s">
@@ -19632,7 +19632,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="29" t="s">
         <v>443</v>
       </c>
       <c r="B3" t="s">
@@ -19643,7 +19643,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>444</v>
       </c>
       <c r="B4" t="s">
@@ -19654,7 +19654,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="29" t="s">
         <v>445</v>
       </c>
       <c r="B5" t="s">
@@ -19665,7 +19665,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="29" t="s">
         <v>446</v>
       </c>
       <c r="B6" t="s">
@@ -19676,7 +19676,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>447</v>
       </c>
       <c r="B7" t="s">
@@ -19687,7 +19687,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="29" t="s">
         <v>448</v>
       </c>
       <c r="B8" t="s">
@@ -19698,7 +19698,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="29" t="s">
         <v>449</v>
       </c>
       <c r="B9" t="s">
@@ -19709,7 +19709,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="29" t="s">
         <v>450</v>
       </c>
       <c r="B10" t="s">
@@ -19720,7 +19720,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="29" t="s">
         <v>451</v>
       </c>
       <c r="B11" t="s">
@@ -19731,7 +19731,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>452</v>
       </c>
       <c r="B12" t="s">
@@ -19742,7 +19742,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="29" t="s">
         <v>453</v>
       </c>
       <c r="B13" t="s">
@@ -19753,7 +19753,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="29" t="s">
         <v>454</v>
       </c>
       <c r="B14" t="s">
@@ -19764,7 +19764,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="29" t="s">
         <v>455</v>
       </c>
       <c r="B15" t="s">
@@ -19775,7 +19775,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="29" t="s">
         <v>456</v>
       </c>
       <c r="B16" t="s">
@@ -19786,7 +19786,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="29" t="s">
         <v>457</v>
       </c>
       <c r="B17" t="s">
@@ -19797,7 +19797,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>458</v>
       </c>
       <c r="B18" t="s">
@@ -19808,7 +19808,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="29" t="s">
         <v>459</v>
       </c>
       <c r="B19" t="s">
@@ -19819,7 +19819,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="29" t="s">
         <v>460</v>
       </c>
       <c r="B20" t="s">
@@ -19830,7 +19830,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="29" t="s">
         <v>461</v>
       </c>
       <c r="B21" t="s">
@@ -19841,10 +19841,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+      <c r="A22" s="28"/>
     </row>
     <row r="23" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="29" t="s">
         <v>462</v>
       </c>
       <c r="B23" t="s">
@@ -19855,7 +19855,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="29" t="s">
         <v>463</v>
       </c>
       <c r="B24" t="s">
@@ -19866,7 +19866,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="29" t="s">
         <v>464</v>
       </c>
       <c r="B25" t="s">
@@ -19877,7 +19877,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="29" t="s">
         <v>465</v>
       </c>
       <c r="B26" t="s">
@@ -19888,7 +19888,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="29" t="s">
         <v>466</v>
       </c>
       <c r="B27" t="s">
@@ -19899,7 +19899,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="29" t="s">
         <v>467</v>
       </c>
       <c r="B28" t="s">
@@ -19910,7 +19910,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="29" t="s">
         <v>468</v>
       </c>
       <c r="B29" t="s">
@@ -19921,7 +19921,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="29" t="s">
         <v>469</v>
       </c>
       <c r="B30" t="s">
@@ -19932,7 +19932,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="29" t="s">
         <v>470</v>
       </c>
       <c r="B31" t="s">
@@ -19943,7 +19943,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="29" t="s">
         <v>471</v>
       </c>
       <c r="B32" t="s">
@@ -19954,7 +19954,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="29" t="s">
         <v>472</v>
       </c>
       <c r="B33" t="s">
@@ -19965,7 +19965,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="29" t="s">
         <v>473</v>
       </c>
       <c r="B34" t="s">
@@ -19976,7 +19976,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="29" t="s">
         <v>474</v>
       </c>
       <c r="B35" t="s">
@@ -19987,7 +19987,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="29" t="s">
         <v>475</v>
       </c>
       <c r="B36" t="s">
@@ -19998,7 +19998,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="29" t="s">
         <v>476</v>
       </c>
       <c r="B37" t="s">
@@ -20009,7 +20009,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="29" t="s">
         <v>477</v>
       </c>
       <c r="B38" t="s">
@@ -20020,7 +20020,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="29" t="s">
         <v>478</v>
       </c>
       <c r="B39" t="s">
@@ -20031,7 +20031,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="29" t="s">
         <v>479</v>
       </c>
       <c r="B40" t="s">
@@ -20042,7 +20042,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="29" t="s">
         <v>480</v>
       </c>
       <c r="B41" t="s">
@@ -20053,7 +20053,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="29" t="s">
         <v>481</v>
       </c>
       <c r="B42" t="s">
@@ -20064,7 +20064,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="29" t="s">
         <v>482</v>
       </c>
       <c r="B43" t="s">
@@ -20075,7 +20075,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="29" t="s">
         <v>483</v>
       </c>
       <c r="B44" t="s">
@@ -20086,7 +20086,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="29" t="s">
         <v>484</v>
       </c>
       <c r="B45" t="s">
@@ -20097,7 +20097,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="29" t="s">
         <v>485</v>
       </c>
       <c r="B46" t="s">
@@ -20108,7 +20108,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="29" t="s">
         <v>486</v>
       </c>
       <c r="B47" t="s">
@@ -20119,7 +20119,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="29" t="s">
         <v>487</v>
       </c>
       <c r="B48" t="s">
@@ -20130,7 +20130,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="29" t="s">
         <v>488</v>
       </c>
       <c r="B49" t="s">
@@ -20141,7 +20141,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="29" t="s">
         <v>489</v>
       </c>
       <c r="B50" t="s">
@@ -20152,7 +20152,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="29" t="s">
         <v>490</v>
       </c>
       <c r="B51" t="s">
@@ -20163,10 +20163,10 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
+      <c r="A52" s="28"/>
     </row>
     <row r="53" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="29" t="s">
         <v>491</v>
       </c>
       <c r="B53" t="s">
@@ -20177,7 +20177,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="29" t="s">
         <v>492</v>
       </c>
       <c r="B54" t="s">
@@ -20188,7 +20188,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="29" t="s">
         <v>493</v>
       </c>
       <c r="B55" t="s">
@@ -20199,7 +20199,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="29" t="s">
         <v>494</v>
       </c>
       <c r="B56" t="s">
@@ -20210,7 +20210,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="29" t="s">
         <v>495</v>
       </c>
       <c r="B57" t="s">
@@ -20221,7 +20221,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="29" t="s">
         <v>496</v>
       </c>
       <c r="B58" t="s">
@@ -20232,7 +20232,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="29" t="s">
         <v>497</v>
       </c>
       <c r="B59" t="s">
@@ -20243,7 +20243,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="29" t="s">
         <v>498</v>
       </c>
       <c r="B60" t="s">
@@ -20254,7 +20254,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="29" t="s">
         <v>499</v>
       </c>
       <c r="B61" t="s">
@@ -20265,7 +20265,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="29" t="s">
         <v>500</v>
       </c>
       <c r="B62" t="s">
@@ -20276,7 +20276,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="29" t="s">
         <v>501</v>
       </c>
       <c r="B63" t="s">
@@ -20287,7 +20287,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="29" t="s">
         <v>502</v>
       </c>
       <c r="B64" t="s">
@@ -20298,7 +20298,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="29" t="s">
         <v>503</v>
       </c>
       <c r="B65" t="s">
@@ -20309,7 +20309,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="29" t="s">
         <v>504</v>
       </c>
       <c r="B66" t="s">
@@ -20320,7 +20320,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="29" t="s">
         <v>505</v>
       </c>
       <c r="B67" t="s">
@@ -20331,7 +20331,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="29" t="s">
         <v>506</v>
       </c>
       <c r="B68" t="s">
@@ -20342,7 +20342,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="29" t="s">
         <v>507</v>
       </c>
       <c r="B69" t="s">
@@ -20353,7 +20353,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="29" t="s">
         <v>508</v>
       </c>
       <c r="B70" t="s">
@@ -20364,7 +20364,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="29" t="s">
         <v>509</v>
       </c>
       <c r="B71" t="s">
@@ -20375,7 +20375,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="29" t="s">
         <v>510</v>
       </c>
       <c r="B72" t="s">
@@ -20386,7 +20386,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
+      <c r="A73" s="29" t="s">
         <v>511</v>
       </c>
       <c r="B73" t="s">
@@ -20397,7 +20397,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="29" t="s">
         <v>512</v>
       </c>
       <c r="B74" t="s">
@@ -20408,10 +20408,10 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="30"/>
+      <c r="A75" s="28"/>
     </row>
     <row r="76" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="29" t="s">
         <v>513</v>
       </c>
       <c r="B76" t="s">
@@ -20422,7 +20422,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="29" t="s">
         <v>514</v>
       </c>
       <c r="B77" t="s">
@@ -20433,7 +20433,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="31" t="s">
+      <c r="A78" s="29" t="s">
         <v>515</v>
       </c>
       <c r="B78" t="s">
@@ -20444,7 +20444,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="31" t="s">
+      <c r="A79" s="29" t="s">
         <v>516</v>
       </c>
       <c r="B79" t="s">
@@ -20455,7 +20455,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="31" t="s">
+      <c r="A80" s="29" t="s">
         <v>517</v>
       </c>
       <c r="B80" t="s">
@@ -20466,7 +20466,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="31" t="s">
+      <c r="A81" s="29" t="s">
         <v>518</v>
       </c>
       <c r="B81" t="s">
@@ -20477,7 +20477,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="29" t="s">
         <v>519</v>
       </c>
       <c r="B82" t="s">
@@ -20488,7 +20488,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="31" t="s">
+      <c r="A83" s="29" t="s">
         <v>520</v>
       </c>
       <c r="B83" t="s">
@@ -20499,7 +20499,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="31" t="s">
+      <c r="A84" s="29" t="s">
         <v>521</v>
       </c>
       <c r="B84" t="s">
@@ -20510,7 +20510,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="31" t="s">
+      <c r="A85" s="29" t="s">
         <v>522</v>
       </c>
       <c r="B85" t="s">
@@ -20521,7 +20521,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="29" t="s">
         <v>523</v>
       </c>
       <c r="B86" t="s">
@@ -20532,10 +20532,10 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="30"/>
+      <c r="A87" s="28"/>
     </row>
     <row r="88" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="31" t="s">
+      <c r="A88" s="29" t="s">
         <v>524</v>
       </c>
       <c r="B88" t="s">
@@ -20546,7 +20546,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="31" t="s">
+      <c r="A89" s="29" t="s">
         <v>525</v>
       </c>
       <c r="B89" t="s">
@@ -20557,7 +20557,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="31" t="s">
+      <c r="A90" s="29" t="s">
         <v>526</v>
       </c>
       <c r="B90" t="s">
@@ -20568,7 +20568,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="31" t="s">
+      <c r="A91" s="29" t="s">
         <v>527</v>
       </c>
       <c r="B91" t="s">
@@ -20579,7 +20579,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="31" t="s">
+      <c r="A92" s="29" t="s">
         <v>528</v>
       </c>
       <c r="B92" t="s">
@@ -20590,7 +20590,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="31" t="s">
+      <c r="A93" s="29" t="s">
         <v>529</v>
       </c>
       <c r="B93" t="s">
@@ -20601,7 +20601,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="31" t="s">
+      <c r="A94" s="29" t="s">
         <v>530</v>
       </c>
       <c r="B94" t="s">
@@ -20612,7 +20612,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="29" t="s">
         <v>531</v>
       </c>
       <c r="B95" t="s">
@@ -20623,7 +20623,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
+      <c r="A96" s="29" t="s">
         <v>532</v>
       </c>
       <c r="B96" t="s">
@@ -20634,7 +20634,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="31" t="s">
+      <c r="A97" s="29" t="s">
         <v>533</v>
       </c>
       <c r="B97" t="s">
@@ -20645,7 +20645,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
+      <c r="A98" s="29" t="s">
         <v>534</v>
       </c>
       <c r="B98" t="s">
@@ -20656,7 +20656,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="31" t="s">
+      <c r="A99" s="29" t="s">
         <v>535</v>
       </c>
       <c r="B99" t="s">
@@ -20667,7 +20667,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="31" t="s">
+      <c r="A100" s="29" t="s">
         <v>536</v>
       </c>
       <c r="B100" t="s">
@@ -20678,7 +20678,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="31" t="s">
+      <c r="A101" s="29" t="s">
         <v>537</v>
       </c>
       <c r="B101" t="s">
@@ -20689,10 +20689,10 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="30"/>
+      <c r="A102" s="28"/>
     </row>
     <row r="103" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="31" t="s">
+      <c r="A103" s="29" t="s">
         <v>538</v>
       </c>
       <c r="B103" t="s">
@@ -20703,7 +20703,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="31" t="s">
+      <c r="A104" s="29" t="s">
         <v>539</v>
       </c>
       <c r="B104" t="s">
@@ -20714,7 +20714,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="31" t="s">
+      <c r="A105" s="29" t="s">
         <v>540</v>
       </c>
       <c r="B105" t="s">
@@ -20725,7 +20725,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="31" t="s">
+      <c r="A106" s="29" t="s">
         <v>541</v>
       </c>
       <c r="B106" t="s">
@@ -20736,7 +20736,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="31" t="s">
+      <c r="A107" s="29" t="s">
         <v>542</v>
       </c>
       <c r="B107" t="s">
@@ -20747,7 +20747,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="31" t="s">
+      <c r="A108" s="29" t="s">
         <v>543</v>
       </c>
       <c r="B108" t="s">
@@ -20758,7 +20758,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="31" t="s">
+      <c r="A109" s="29" t="s">
         <v>544</v>
       </c>
       <c r="B109" t="s">
@@ -20769,7 +20769,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="31" t="s">
+      <c r="A110" s="29" t="s">
         <v>545</v>
       </c>
       <c r="B110" t="s">
@@ -20780,7 +20780,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="31" t="s">
+      <c r="A111" s="29" t="s">
         <v>546</v>
       </c>
       <c r="B111" t="s">
@@ -20791,7 +20791,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="31" t="s">
+      <c r="A112" s="29" t="s">
         <v>547</v>
       </c>
       <c r="B112" t="s">
@@ -20802,7 +20802,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="31" t="s">
+      <c r="A113" s="29" t="s">
         <v>548</v>
       </c>
       <c r="B113" t="s">
@@ -20813,7 +20813,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="31" t="s">
+      <c r="A114" s="29" t="s">
         <v>549</v>
       </c>
       <c r="B114" t="s">
@@ -20824,7 +20824,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="31" t="s">
+      <c r="A115" s="29" t="s">
         <v>550</v>
       </c>
       <c r="B115" t="s">
@@ -20835,7 +20835,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="31" t="s">
+      <c r="A116" s="29" t="s">
         <v>551</v>
       </c>
       <c r="B116" t="s">
@@ -20846,7 +20846,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="31" t="s">
+      <c r="A117" s="29" t="s">
         <v>552</v>
       </c>
       <c r="B117" t="s">
@@ -20857,7 +20857,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="31" t="s">
+      <c r="A118" s="29" t="s">
         <v>553</v>
       </c>
       <c r="B118" t="s">
@@ -20868,7 +20868,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="31" t="s">
+      <c r="A119" s="29" t="s">
         <v>554</v>
       </c>
       <c r="B119" t="s">
@@ -20879,10 +20879,10 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="30"/>
+      <c r="A120" s="28"/>
     </row>
     <row r="121" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="31" t="s">
+      <c r="A121" s="29" t="s">
         <v>555</v>
       </c>
       <c r="B121" t="s">
@@ -20893,7 +20893,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="31" t="s">
+      <c r="A122" s="29" t="s">
         <v>556</v>
       </c>
       <c r="B122" t="s">
@@ -20904,7 +20904,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="31" t="s">
+      <c r="A123" s="29" t="s">
         <v>557</v>
       </c>
       <c r="B123" t="s">
@@ -20915,7 +20915,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="31" t="s">
+      <c r="A124" s="29" t="s">
         <v>558</v>
       </c>
       <c r="B124" t="s">
@@ -20926,7 +20926,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="31" t="s">
+      <c r="A125" s="29" t="s">
         <v>559</v>
       </c>
       <c r="B125" t="s">
@@ -20937,7 +20937,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="31" t="s">
+      <c r="A126" s="29" t="s">
         <v>560</v>
       </c>
       <c r="B126" t="s">
@@ -20948,7 +20948,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="31" t="s">
+      <c r="A127" s="29" t="s">
         <v>561</v>
       </c>
       <c r="B127" t="s">
@@ -20959,7 +20959,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="31" t="s">
+      <c r="A128" s="29" t="s">
         <v>562</v>
       </c>
       <c r="B128" t="s">
@@ -20970,7 +20970,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="31" t="s">
+      <c r="A129" s="29" t="s">
         <v>563</v>
       </c>
       <c r="B129" t="s">
@@ -20981,7 +20981,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="31" t="s">
+      <c r="A130" s="29" t="s">
         <v>564</v>
       </c>
       <c r="B130" t="s">
@@ -20992,7 +20992,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="31" t="s">
+      <c r="A131" s="29" t="s">
         <v>565</v>
       </c>
       <c r="B131" t="s">
@@ -21003,7 +21003,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="31" t="s">
+      <c r="A132" s="29" t="s">
         <v>566</v>
       </c>
       <c r="B132" t="s">
@@ -21014,7 +21014,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="31" t="s">
+      <c r="A133" s="29" t="s">
         <v>567</v>
       </c>
       <c r="B133" t="s">
@@ -21025,7 +21025,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="31" t="s">
+      <c r="A134" s="29" t="s">
         <v>568</v>
       </c>
       <c r="B134" t="s">
@@ -21036,7 +21036,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="31" t="s">
+      <c r="A135" s="29" t="s">
         <v>569</v>
       </c>
       <c r="B135" t="s">
@@ -21047,7 +21047,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="31" t="s">
+      <c r="A136" s="29" t="s">
         <v>570</v>
       </c>
       <c r="B136" t="s">
@@ -21058,7 +21058,7 @@
       </c>
     </row>
     <row r="137" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="31" t="s">
+      <c r="A137" s="29" t="s">
         <v>571</v>
       </c>
       <c r="B137" t="s">
@@ -21069,10 +21069,10 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="30"/>
+      <c r="A138" s="28"/>
     </row>
     <row r="139" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="31" t="s">
+      <c r="A139" s="29" t="s">
         <v>572</v>
       </c>
       <c r="B139" t="s">
@@ -21083,7 +21083,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="31" t="s">
+      <c r="A140" s="29" t="s">
         <v>573</v>
       </c>
       <c r="B140" t="s">
@@ -21094,7 +21094,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="31" t="s">
+      <c r="A141" s="29" t="s">
         <v>574</v>
       </c>
       <c r="B141" t="s">
@@ -21105,7 +21105,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="31" t="s">
+      <c r="A142" s="29" t="s">
         <v>575</v>
       </c>
       <c r="B142" t="s">
@@ -21116,7 +21116,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="31" t="s">
+      <c r="A143" s="29" t="s">
         <v>576</v>
       </c>
       <c r="B143" t="s">
@@ -21127,7 +21127,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="31" t="s">
+      <c r="A144" s="29" t="s">
         <v>577</v>
       </c>
       <c r="B144" t="s">
@@ -21138,7 +21138,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="31" t="s">
+      <c r="A145" s="29" t="s">
         <v>578</v>
       </c>
       <c r="B145" t="s">
@@ -21149,7 +21149,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="31" t="s">
+      <c r="A146" s="29" t="s">
         <v>579</v>
       </c>
       <c r="B146" t="s">
@@ -21160,7 +21160,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="31" t="s">
+      <c r="A147" s="29" t="s">
         <v>580</v>
       </c>
       <c r="B147" t="s">
@@ -21171,7 +21171,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="31" t="s">
+      <c r="A148" s="29" t="s">
         <v>581</v>
       </c>
       <c r="B148" t="s">
@@ -21182,7 +21182,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="31" t="s">
+      <c r="A149" s="29" t="s">
         <v>582</v>
       </c>
       <c r="B149" t="s">
@@ -21193,7 +21193,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="31" t="s">
+      <c r="A150" s="29" t="s">
         <v>583</v>
       </c>
       <c r="B150" t="s">
@@ -21204,7 +21204,7 @@
       </c>
     </row>
     <row r="151" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="31" t="s">
+      <c r="A151" s="29" t="s">
         <v>584</v>
       </c>
       <c r="B151" t="s">
@@ -21215,10 +21215,10 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="30"/>
+      <c r="A152" s="28"/>
     </row>
     <row r="153" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="31" t="s">
+      <c r="A153" s="29" t="s">
         <v>585</v>
       </c>
       <c r="B153" t="s">
@@ -21229,7 +21229,7 @@
       </c>
     </row>
     <row r="154" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="31" t="s">
+      <c r="A154" s="29" t="s">
         <v>586</v>
       </c>
       <c r="B154" t="s">
@@ -21240,7 +21240,7 @@
       </c>
     </row>
     <row r="155" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="31" t="s">
+      <c r="A155" s="29" t="s">
         <v>587</v>
       </c>
       <c r="B155" t="s">
@@ -21251,7 +21251,7 @@
       </c>
     </row>
     <row r="156" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="31" t="s">
+      <c r="A156" s="29" t="s">
         <v>588</v>
       </c>
       <c r="B156" t="s">
@@ -21262,7 +21262,7 @@
       </c>
     </row>
     <row r="157" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="31" t="s">
+      <c r="A157" s="29" t="s">
         <v>589</v>
       </c>
       <c r="B157" t="s">
@@ -21273,7 +21273,7 @@
       </c>
     </row>
     <row r="158" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="31" t="s">
+      <c r="A158" s="29" t="s">
         <v>590</v>
       </c>
       <c r="B158" t="s">
@@ -21284,7 +21284,7 @@
       </c>
     </row>
     <row r="159" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="31" t="s">
+      <c r="A159" s="29" t="s">
         <v>591</v>
       </c>
       <c r="B159" t="s">
@@ -21295,7 +21295,7 @@
       </c>
     </row>
     <row r="160" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="31" t="s">
+      <c r="A160" s="29" t="s">
         <v>592</v>
       </c>
       <c r="B160" t="s">
@@ -21306,7 +21306,7 @@
       </c>
     </row>
     <row r="161" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="31" t="s">
+      <c r="A161" s="29" t="s">
         <v>593</v>
       </c>
       <c r="B161" t="s">
@@ -21317,7 +21317,7 @@
       </c>
     </row>
     <row r="162" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="31" t="s">
+      <c r="A162" s="29" t="s">
         <v>594</v>
       </c>
       <c r="B162" t="s">
@@ -21328,7 +21328,7 @@
       </c>
     </row>
     <row r="163" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A163" s="31" t="s">
+      <c r="A163" s="29" t="s">
         <v>595</v>
       </c>
       <c r="B163" t="s">
@@ -21339,7 +21339,7 @@
       </c>
     </row>
     <row r="164" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="31" t="s">
+      <c r="A164" s="29" t="s">
         <v>596</v>
       </c>
       <c r="B164" t="s">
@@ -21350,7 +21350,7 @@
       </c>
     </row>
     <row r="165" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="31" t="s">
+      <c r="A165" s="29" t="s">
         <v>597</v>
       </c>
       <c r="B165" t="s">
@@ -21361,7 +21361,7 @@
       </c>
     </row>
     <row r="166" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="31" t="s">
+      <c r="A166" s="29" t="s">
         <v>598</v>
       </c>
       <c r="B166" t="s">
@@ -21372,7 +21372,7 @@
       </c>
     </row>
     <row r="167" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="31" t="s">
+      <c r="A167" s="29" t="s">
         <v>599</v>
       </c>
       <c r="B167" t="s">
@@ -21383,7 +21383,7 @@
       </c>
     </row>
     <row r="168" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="31" t="s">
+      <c r="A168" s="29" t="s">
         <v>600</v>
       </c>
       <c r="B168" t="s">
@@ -21394,7 +21394,7 @@
       </c>
     </row>
     <row r="169" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A169" s="31" t="s">
+      <c r="A169" s="29" t="s">
         <v>601</v>
       </c>
       <c r="B169" t="s">
@@ -21405,7 +21405,7 @@
       </c>
     </row>
     <row r="170" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="31" t="s">
+      <c r="A170" s="29" t="s">
         <v>602</v>
       </c>
       <c r="B170" t="s">
@@ -21416,7 +21416,7 @@
       </c>
     </row>
     <row r="171" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="31" t="s">
+      <c r="A171" s="29" t="s">
         <v>603</v>
       </c>
       <c r="B171" t="s">
@@ -21427,7 +21427,7 @@
       </c>
     </row>
     <row r="172" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="31" t="s">
+      <c r="A172" s="29" t="s">
         <v>604</v>
       </c>
       <c r="B172" t="s">
@@ -21438,7 +21438,7 @@
       </c>
     </row>
     <row r="173" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="31" t="s">
+      <c r="A173" s="29" t="s">
         <v>605</v>
       </c>
       <c r="B173" t="s">
@@ -21449,10 +21449,10 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="30"/>
+      <c r="A174" s="28"/>
     </row>
     <row r="175" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="31" t="s">
+      <c r="A175" s="29" t="s">
         <v>606</v>
       </c>
       <c r="B175" t="s">
@@ -21463,7 +21463,7 @@
       </c>
     </row>
     <row r="176" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="31" t="s">
+      <c r="A176" s="29" t="s">
         <v>607</v>
       </c>
       <c r="B176" t="s">
@@ -21474,7 +21474,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="31" t="s">
+      <c r="A177" s="29" t="s">
         <v>608</v>
       </c>
       <c r="B177" t="s">
@@ -21485,7 +21485,7 @@
       </c>
     </row>
     <row r="178" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="31" t="s">
+      <c r="A178" s="29" t="s">
         <v>609</v>
       </c>
       <c r="B178" t="s">
@@ -21496,7 +21496,7 @@
       </c>
     </row>
     <row r="179" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="31" t="s">
+      <c r="A179" s="29" t="s">
         <v>610</v>
       </c>
       <c r="B179" t="s">
@@ -21507,7 +21507,7 @@
       </c>
     </row>
     <row r="180" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A180" s="31" t="s">
+      <c r="A180" s="29" t="s">
         <v>611</v>
       </c>
       <c r="B180" t="s">
@@ -21518,7 +21518,7 @@
       </c>
     </row>
     <row r="181" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A181" s="31" t="s">
+      <c r="A181" s="29" t="s">
         <v>612</v>
       </c>
       <c r="B181" t="s">
@@ -21529,7 +21529,7 @@
       </c>
     </row>
     <row r="182" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="31" t="s">
+      <c r="A182" s="29" t="s">
         <v>613</v>
       </c>
       <c r="B182" t="s">
@@ -21540,7 +21540,7 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="31" t="s">
+      <c r="A183" s="29" t="s">
         <v>614</v>
       </c>
       <c r="B183" t="s">
@@ -21551,7 +21551,7 @@
       </c>
     </row>
     <row r="184" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="31" t="s">
+      <c r="A184" s="29" t="s">
         <v>615</v>
       </c>
       <c r="B184" t="s">
@@ -21562,7 +21562,7 @@
       </c>
     </row>
     <row r="185" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A185" s="31" t="s">
+      <c r="A185" s="29" t="s">
         <v>616</v>
       </c>
       <c r="B185" t="s">
@@ -21573,10 +21573,10 @@
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="30"/>
+      <c r="A186" s="28"/>
     </row>
     <row r="187" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A187" s="31" t="s">
+      <c r="A187" s="29" t="s">
         <v>617</v>
       </c>
       <c r="B187" t="s">
@@ -21587,7 +21587,7 @@
       </c>
     </row>
     <row r="188" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="31" t="s">
+      <c r="A188" s="29" t="s">
         <v>618</v>
       </c>
       <c r="B188" t="s">
@@ -21598,7 +21598,7 @@
       </c>
     </row>
     <row r="189" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A189" s="31" t="s">
+      <c r="A189" s="29" t="s">
         <v>619</v>
       </c>
       <c r="B189" t="s">
@@ -21609,7 +21609,7 @@
       </c>
     </row>
     <row r="190" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="31" t="s">
+      <c r="A190" s="29" t="s">
         <v>620</v>
       </c>
       <c r="B190" t="s">
@@ -21620,7 +21620,7 @@
       </c>
     </row>
     <row r="191" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A191" s="31" t="s">
+      <c r="A191" s="29" t="s">
         <v>621</v>
       </c>
       <c r="B191" t="s">
@@ -21631,7 +21631,7 @@
       </c>
     </row>
     <row r="192" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A192" s="31" t="s">
+      <c r="A192" s="29" t="s">
         <v>622</v>
       </c>
       <c r="B192" t="s">
@@ -21642,7 +21642,7 @@
       </c>
     </row>
     <row r="193" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A193" s="31" t="s">
+      <c r="A193" s="29" t="s">
         <v>623</v>
       </c>
       <c r="B193" t="s">
@@ -21653,7 +21653,7 @@
       </c>
     </row>
     <row r="194" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="31" t="s">
+      <c r="A194" s="29" t="s">
         <v>624</v>
       </c>
       <c r="B194" t="s">
@@ -21664,7 +21664,7 @@
       </c>
     </row>
     <row r="195" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A195" s="31" t="s">
+      <c r="A195" s="29" t="s">
         <v>625</v>
       </c>
       <c r="B195" t="s">
@@ -21675,7 +21675,7 @@
       </c>
     </row>
     <row r="196" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="31" t="s">
+      <c r="A196" s="29" t="s">
         <v>626</v>
       </c>
       <c r="B196" t="s">
@@ -21686,7 +21686,7 @@
       </c>
     </row>
     <row r="197" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A197" s="31" t="s">
+      <c r="A197" s="29" t="s">
         <v>627</v>
       </c>
       <c r="B197" t="s">
@@ -21697,7 +21697,7 @@
       </c>
     </row>
     <row r="198" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A198" s="31" t="s">
+      <c r="A198" s="29" t="s">
         <v>628</v>
       </c>
       <c r="B198" t="s">
@@ -21708,7 +21708,7 @@
       </c>
     </row>
     <row r="199" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="31" t="s">
+      <c r="A199" s="29" t="s">
         <v>629</v>
       </c>
       <c r="B199" t="s">
@@ -21719,7 +21719,7 @@
       </c>
     </row>
     <row r="200" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A200" s="31" t="s">
+      <c r="A200" s="29" t="s">
         <v>630</v>
       </c>
       <c r="B200" t="s">
@@ -21730,7 +21730,7 @@
       </c>
     </row>
     <row r="201" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="31" t="s">
+      <c r="A201" s="29" t="s">
         <v>631</v>
       </c>
       <c r="B201" t="s">
@@ -21741,7 +21741,7 @@
       </c>
     </row>
     <row r="202" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A202" s="31" t="s">
+      <c r="A202" s="29" t="s">
         <v>632</v>
       </c>
       <c r="B202" t="s">
@@ -21752,7 +21752,7 @@
       </c>
     </row>
     <row r="203" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="31" t="s">
+      <c r="A203" s="29" t="s">
         <v>633</v>
       </c>
       <c r="B203" t="s">
@@ -21763,7 +21763,7 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="31" t="s">
+      <c r="A204" s="29" t="s">
         <v>634</v>
       </c>
       <c r="B204" t="s">
@@ -21774,7 +21774,7 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A205" s="31" t="s">
+      <c r="A205" s="29" t="s">
         <v>635</v>
       </c>
       <c r="B205" t="s">
@@ -21785,10 +21785,10 @@
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="30"/>
+      <c r="A206" s="28"/>
     </row>
     <row r="207" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="31" t="s">
+      <c r="A207" s="29" t="s">
         <v>636</v>
       </c>
       <c r="B207" t="s">
@@ -21799,7 +21799,7 @@
       </c>
     </row>
     <row r="208" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="31" t="s">
+      <c r="A208" s="29" t="s">
         <v>637</v>
       </c>
       <c r="B208" t="s">
@@ -21810,7 +21810,7 @@
       </c>
     </row>
     <row r="209" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A209" s="31" t="s">
+      <c r="A209" s="29" t="s">
         <v>638</v>
       </c>
       <c r="B209" t="s">
@@ -21821,7 +21821,7 @@
       </c>
     </row>
     <row r="210" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="31" t="s">
+      <c r="A210" s="29" t="s">
         <v>639</v>
       </c>
       <c r="B210" t="s">
@@ -21832,7 +21832,7 @@
       </c>
     </row>
     <row r="211" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="31" t="s">
+      <c r="A211" s="29" t="s">
         <v>640</v>
       </c>
       <c r="B211" t="s">
@@ -21843,7 +21843,7 @@
       </c>
     </row>
     <row r="212" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="31" t="s">
+      <c r="A212" s="29" t="s">
         <v>641</v>
       </c>
       <c r="B212" t="s">
@@ -21854,7 +21854,7 @@
       </c>
     </row>
     <row r="213" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A213" s="31" t="s">
+      <c r="A213" s="29" t="s">
         <v>642</v>
       </c>
       <c r="B213" t="s">
@@ -21865,7 +21865,7 @@
       </c>
     </row>
     <row r="214" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="31" t="s">
+      <c r="A214" s="29" t="s">
         <v>643</v>
       </c>
       <c r="B214" t="s">
@@ -21876,7 +21876,7 @@
       </c>
     </row>
     <row r="215" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A215" s="31" t="s">
+      <c r="A215" s="29" t="s">
         <v>644</v>
       </c>
       <c r="B215" t="s">
@@ -21887,7 +21887,7 @@
       </c>
     </row>
     <row r="216" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="31" t="s">
+      <c r="A216" s="29" t="s">
         <v>645</v>
       </c>
       <c r="B216" t="s">
@@ -21898,7 +21898,7 @@
       </c>
     </row>
     <row r="217" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A217" s="31" t="s">
+      <c r="A217" s="29" t="s">
         <v>646</v>
       </c>
       <c r="B217" t="s">
@@ -21909,7 +21909,7 @@
       </c>
     </row>
     <row r="218" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A218" s="31" t="s">
+      <c r="A218" s="29" t="s">
         <v>647</v>
       </c>
       <c r="B218" t="s">
@@ -21920,7 +21920,7 @@
       </c>
     </row>
     <row r="219" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A219" s="31" t="s">
+      <c r="A219" s="29" t="s">
         <v>648</v>
       </c>
       <c r="B219" t="s">
@@ -21931,7 +21931,7 @@
       </c>
     </row>
     <row r="220" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A220" s="31" t="s">
+      <c r="A220" s="29" t="s">
         <v>649</v>
       </c>
       <c r="B220" t="s">
@@ -21942,7 +21942,7 @@
       </c>
     </row>
     <row r="221" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A221" s="31" t="s">
+      <c r="A221" s="29" t="s">
         <v>650</v>
       </c>
       <c r="B221" t="s">
@@ -21953,7 +21953,7 @@
       </c>
     </row>
     <row r="222" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="31" t="s">
+      <c r="A222" s="29" t="s">
         <v>651</v>
       </c>
       <c r="B222" t="s">
@@ -21964,7 +21964,7 @@
       </c>
     </row>
     <row r="223" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A223" s="31" t="s">
+      <c r="A223" s="29" t="s">
         <v>652</v>
       </c>
       <c r="B223" t="s">
@@ -21975,7 +21975,7 @@
       </c>
     </row>
     <row r="224" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A224" s="31" t="s">
+      <c r="A224" s="29" t="s">
         <v>653</v>
       </c>
       <c r="B224" t="s">
@@ -21986,10 +21986,10 @@
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="30"/>
+      <c r="A225" s="28"/>
     </row>
     <row r="226" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A226" s="31" t="s">
+      <c r="A226" s="29" t="s">
         <v>654</v>
       </c>
       <c r="B226" t="s">
@@ -22000,7 +22000,7 @@
       </c>
     </row>
     <row r="227" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A227" s="31" t="s">
+      <c r="A227" s="29" t="s">
         <v>655</v>
       </c>
       <c r="B227" t="s">
@@ -22011,7 +22011,7 @@
       </c>
     </row>
     <row r="228" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A228" s="31" t="s">
+      <c r="A228" s="29" t="s">
         <v>656</v>
       </c>
       <c r="B228" t="s">
@@ -22022,7 +22022,7 @@
       </c>
     </row>
     <row r="229" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A229" s="31" t="s">
+      <c r="A229" s="29" t="s">
         <v>657</v>
       </c>
       <c r="B229" t="s">
@@ -22033,7 +22033,7 @@
       </c>
     </row>
     <row r="230" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A230" s="31" t="s">
+      <c r="A230" s="29" t="s">
         <v>658</v>
       </c>
       <c r="B230" t="s">
@@ -22044,7 +22044,7 @@
       </c>
     </row>
     <row r="231" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A231" s="31" t="s">
+      <c r="A231" s="29" t="s">
         <v>659</v>
       </c>
       <c r="B231" t="s">
@@ -22055,7 +22055,7 @@
       </c>
     </row>
     <row r="232" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A232" s="31" t="s">
+      <c r="A232" s="29" t="s">
         <v>660</v>
       </c>
       <c r="B232" t="s">
@@ -22066,7 +22066,7 @@
       </c>
     </row>
     <row r="233" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A233" s="31" t="s">
+      <c r="A233" s="29" t="s">
         <v>661</v>
       </c>
       <c r="B233" t="s">
@@ -22077,7 +22077,7 @@
       </c>
     </row>
     <row r="234" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A234" s="31" t="s">
+      <c r="A234" s="29" t="s">
         <v>662</v>
       </c>
       <c r="B234" t="s">
@@ -22088,7 +22088,7 @@
       </c>
     </row>
     <row r="235" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A235" s="31" t="s">
+      <c r="A235" s="29" t="s">
         <v>663</v>
       </c>
       <c r="B235" t="s">
@@ -22099,7 +22099,7 @@
       </c>
     </row>
     <row r="236" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A236" s="31" t="s">
+      <c r="A236" s="29" t="s">
         <v>664</v>
       </c>
       <c r="B236" t="s">
@@ -22110,7 +22110,7 @@
       </c>
     </row>
     <row r="237" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A237" s="31" t="s">
+      <c r="A237" s="29" t="s">
         <v>665</v>
       </c>
       <c r="B237" t="s">
@@ -22121,7 +22121,7 @@
       </c>
     </row>
     <row r="238" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="31" t="s">
+      <c r="A238" s="29" t="s">
         <v>666</v>
       </c>
       <c r="B238" t="s">
@@ -22132,7 +22132,7 @@
       </c>
     </row>
     <row r="239" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="31" t="s">
+      <c r="A239" s="29" t="s">
         <v>667</v>
       </c>
       <c r="B239" t="s">
@@ -22143,7 +22143,7 @@
       </c>
     </row>
     <row r="240" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="31" t="s">
+      <c r="A240" s="29" t="s">
         <v>668</v>
       </c>
       <c r="B240" t="s">
@@ -22154,7 +22154,7 @@
       </c>
     </row>
     <row r="241" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="31" t="s">
+      <c r="A241" s="29" t="s">
         <v>669</v>
       </c>
       <c r="B241" t="s">
@@ -22165,7 +22165,7 @@
       </c>
     </row>
     <row r="242" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="31" t="s">
+      <c r="A242" s="29" t="s">
         <v>670</v>
       </c>
       <c r="B242" t="s">
@@ -22176,7 +22176,7 @@
       </c>
     </row>
     <row r="243" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A243" s="31" t="s">
+      <c r="A243" s="29" t="s">
         <v>671</v>
       </c>
       <c r="B243" t="s">
@@ -22187,10 +22187,10 @@
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="30"/>
+      <c r="A244" s="28"/>
     </row>
     <row r="245" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A245" s="31" t="s">
+      <c r="A245" s="29" t="s">
         <v>672</v>
       </c>
       <c r="B245" t="s">
@@ -22201,7 +22201,7 @@
       </c>
     </row>
     <row r="246" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="31" t="s">
+      <c r="A246" s="29" t="s">
         <v>673</v>
       </c>
       <c r="B246" t="s">
@@ -22212,7 +22212,7 @@
       </c>
     </row>
     <row r="247" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="31" t="s">
+      <c r="A247" s="29" t="s">
         <v>674</v>
       </c>
       <c r="B247" t="s">
@@ -22223,7 +22223,7 @@
       </c>
     </row>
     <row r="248" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="31" t="s">
+      <c r="A248" s="29" t="s">
         <v>675</v>
       </c>
       <c r="B248" t="s">
@@ -22234,7 +22234,7 @@
       </c>
     </row>
     <row r="249" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="31" t="s">
+      <c r="A249" s="29" t="s">
         <v>676</v>
       </c>
       <c r="B249" t="s">
@@ -22245,7 +22245,7 @@
       </c>
     </row>
     <row r="250" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="31" t="s">
+      <c r="A250" s="29" t="s">
         <v>677</v>
       </c>
       <c r="B250" t="s">
@@ -22256,7 +22256,7 @@
       </c>
     </row>
     <row r="251" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="31" t="s">
+      <c r="A251" s="29" t="s">
         <v>678</v>
       </c>
       <c r="B251" t="s">
@@ -22267,7 +22267,7 @@
       </c>
     </row>
     <row r="252" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="31" t="s">
+      <c r="A252" s="29" t="s">
         <v>679</v>
       </c>
       <c r="B252" t="s">
@@ -22278,7 +22278,7 @@
       </c>
     </row>
     <row r="253" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="31" t="s">
+      <c r="A253" s="29" t="s">
         <v>680</v>
       </c>
       <c r="B253" t="s">
@@ -22289,7 +22289,7 @@
       </c>
     </row>
     <row r="254" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="31" t="s">
+      <c r="A254" s="29" t="s">
         <v>681</v>
       </c>
       <c r="B254" t="s">
@@ -22300,7 +22300,7 @@
       </c>
     </row>
     <row r="255" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A255" s="31" t="s">
+      <c r="A255" s="29" t="s">
         <v>682</v>
       </c>
       <c r="B255" t="s">
@@ -22311,7 +22311,7 @@
       </c>
     </row>
     <row r="256" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A256" s="31" t="s">
+      <c r="A256" s="29" t="s">
         <v>683</v>
       </c>
       <c r="B256" t="s">
@@ -22322,7 +22322,7 @@
       </c>
     </row>
     <row r="257" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A257" s="31" t="s">
+      <c r="A257" s="29" t="s">
         <v>684</v>
       </c>
       <c r="B257" t="s">
@@ -22333,7 +22333,7 @@
       </c>
     </row>
     <row r="258" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A258" s="31" t="s">
+      <c r="A258" s="29" t="s">
         <v>685</v>
       </c>
       <c r="B258" t="s">
@@ -22344,7 +22344,7 @@
       </c>
     </row>
     <row r="259" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A259" s="31" t="s">
+      <c r="A259" s="29" t="s">
         <v>686</v>
       </c>
       <c r="B259" t="s">
@@ -22355,7 +22355,7 @@
       </c>
     </row>
     <row r="260" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A260" s="31" t="s">
+      <c r="A260" s="29" t="s">
         <v>687</v>
       </c>
       <c r="B260" t="s">
@@ -22366,7 +22366,7 @@
       </c>
     </row>
     <row r="261" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A261" s="31" t="s">
+      <c r="A261" s="29" t="s">
         <v>688</v>
       </c>
       <c r="B261" t="s">
@@ -22377,7 +22377,7 @@
       </c>
     </row>
     <row r="262" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A262" s="31" t="s">
+      <c r="A262" s="29" t="s">
         <v>689</v>
       </c>
       <c r="B262" t="s">
@@ -22388,7 +22388,7 @@
       </c>
     </row>
     <row r="263" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A263" s="31" t="s">
+      <c r="A263" s="29" t="s">
         <v>690</v>
       </c>
       <c r="B263" t="s">
@@ -22399,7 +22399,7 @@
       </c>
     </row>
     <row r="264" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A264" s="31" t="s">
+      <c r="A264" s="29" t="s">
         <v>691</v>
       </c>
       <c r="B264" t="s">
@@ -22410,10 +22410,10 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="30"/>
+      <c r="A265" s="28"/>
     </row>
     <row r="266" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A266" s="31" t="s">
+      <c r="A266" s="29" t="s">
         <v>692</v>
       </c>
       <c r="B266" t="s">
@@ -22424,7 +22424,7 @@
       </c>
     </row>
     <row r="267" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A267" s="31" t="s">
+      <c r="A267" s="29" t="s">
         <v>693</v>
       </c>
       <c r="B267" t="s">
@@ -22435,7 +22435,7 @@
       </c>
     </row>
     <row r="268" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A268" s="31" t="s">
+      <c r="A268" s="29" t="s">
         <v>694</v>
       </c>
       <c r="B268" t="s">
@@ -22446,7 +22446,7 @@
       </c>
     </row>
     <row r="269" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A269" s="31" t="s">
+      <c r="A269" s="29" t="s">
         <v>695</v>
       </c>
       <c r="B269" t="s">
@@ -22457,7 +22457,7 @@
       </c>
     </row>
     <row r="270" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A270" s="31" t="s">
+      <c r="A270" s="29" t="s">
         <v>696</v>
       </c>
       <c r="B270" t="s">
@@ -22468,7 +22468,7 @@
       </c>
     </row>
     <row r="271" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A271" s="31" t="s">
+      <c r="A271" s="29" t="s">
         <v>697</v>
       </c>
       <c r="B271" t="s">
@@ -22479,7 +22479,7 @@
       </c>
     </row>
     <row r="272" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A272" s="31" t="s">
+      <c r="A272" s="29" t="s">
         <v>698</v>
       </c>
       <c r="B272" t="s">
@@ -22490,7 +22490,7 @@
       </c>
     </row>
     <row r="273" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A273" s="31" t="s">
+      <c r="A273" s="29" t="s">
         <v>699</v>
       </c>
       <c r="B273" t="s">
@@ -22501,10 +22501,10 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="30"/>
+      <c r="A274" s="28"/>
     </row>
     <row r="275" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A275" s="31" t="s">
+      <c r="A275" s="29" t="s">
         <v>700</v>
       </c>
       <c r="B275" t="s">
@@ -22515,7 +22515,7 @@
       </c>
     </row>
     <row r="276" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A276" s="31" t="s">
+      <c r="A276" s="29" t="s">
         <v>701</v>
       </c>
       <c r="B276" t="s">
@@ -22526,7 +22526,7 @@
       </c>
     </row>
     <row r="277" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A277" s="31" t="s">
+      <c r="A277" s="29" t="s">
         <v>702</v>
       </c>
       <c r="B277" t="s">
@@ -22537,7 +22537,7 @@
       </c>
     </row>
     <row r="278" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A278" s="31" t="s">
+      <c r="A278" s="29" t="s">
         <v>703</v>
       </c>
       <c r="B278" t="s">
@@ -22548,7 +22548,7 @@
       </c>
     </row>
     <row r="279" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A279" s="31" t="s">
+      <c r="A279" s="29" t="s">
         <v>704</v>
       </c>
       <c r="B279" t="s">
@@ -22559,7 +22559,7 @@
       </c>
     </row>
     <row r="280" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A280" s="31" t="s">
+      <c r="A280" s="29" t="s">
         <v>705</v>
       </c>
       <c r="B280" t="s">
@@ -22570,7 +22570,7 @@
       </c>
     </row>
     <row r="281" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A281" s="31" t="s">
+      <c r="A281" s="29" t="s">
         <v>706</v>
       </c>
       <c r="B281" t="s">
@@ -22581,7 +22581,7 @@
       </c>
     </row>
     <row r="282" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A282" s="31" t="s">
+      <c r="A282" s="29" t="s">
         <v>707</v>
       </c>
       <c r="B282" t="s">
@@ -22592,7 +22592,7 @@
       </c>
     </row>
     <row r="283" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A283" s="31" t="s">
+      <c r="A283" s="29" t="s">
         <v>708</v>
       </c>
       <c r="B283" t="s">
@@ -22603,7 +22603,7 @@
       </c>
     </row>
     <row r="284" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A284" s="31" t="s">
+      <c r="A284" s="29" t="s">
         <v>709</v>
       </c>
       <c r="B284" t="s">
@@ -22614,7 +22614,7 @@
       </c>
     </row>
     <row r="285" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A285" s="31" t="s">
+      <c r="A285" s="29" t="s">
         <v>710</v>
       </c>
       <c r="B285" t="s">
@@ -22625,7 +22625,7 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A286" s="31" t="s">
+      <c r="A286" s="29" t="s">
         <v>711</v>
       </c>
       <c r="B286" t="s">
@@ -22636,7 +22636,7 @@
       </c>
     </row>
     <row r="287" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A287" s="31" t="s">
+      <c r="A287" s="29" t="s">
         <v>712</v>
       </c>
       <c r="B287" t="s">
@@ -22647,7 +22647,7 @@
       </c>
     </row>
     <row r="288" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A288" s="31" t="s">
+      <c r="A288" s="29" t="s">
         <v>713</v>
       </c>
       <c r="B288" t="s">
@@ -22658,7 +22658,7 @@
       </c>
     </row>
     <row r="289" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A289" s="31" t="s">
+      <c r="A289" s="29" t="s">
         <v>714</v>
       </c>
       <c r="B289" t="s">
@@ -22669,7 +22669,7 @@
       </c>
     </row>
     <row r="290" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A290" s="31" t="s">
+      <c r="A290" s="29" t="s">
         <v>715</v>
       </c>
       <c r="B290" t="s">
@@ -22680,7 +22680,7 @@
       </c>
     </row>
     <row r="291" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A291" s="31" t="s">
+      <c r="A291" s="29" t="s">
         <v>716</v>
       </c>
       <c r="B291" t="s">
@@ -22691,7 +22691,7 @@
       </c>
     </row>
     <row r="292" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A292" s="31" t="s">
+      <c r="A292" s="29" t="s">
         <v>717</v>
       </c>
       <c r="B292" t="s">
@@ -22702,7 +22702,7 @@
       </c>
     </row>
     <row r="293" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A293" s="31" t="s">
+      <c r="A293" s="29" t="s">
         <v>718</v>
       </c>
       <c r="B293" t="s">
@@ -22713,7 +22713,7 @@
       </c>
     </row>
     <row r="294" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A294" s="31" t="s">
+      <c r="A294" s="29" t="s">
         <v>719</v>
       </c>
       <c r="B294" t="s">
@@ -22724,7 +22724,7 @@
       </c>
     </row>
     <row r="295" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A295" s="31" t="s">
+      <c r="A295" s="29" t="s">
         <v>720</v>
       </c>
       <c r="B295" t="s">
@@ -22735,10 +22735,10 @@
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="30"/>
+      <c r="A296" s="28"/>
     </row>
     <row r="297" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A297" s="31" t="s">
+      <c r="A297" s="29" t="s">
         <v>721</v>
       </c>
       <c r="B297" t="s">
@@ -22749,7 +22749,7 @@
       </c>
     </row>
     <row r="298" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A298" s="31" t="s">
+      <c r="A298" s="29" t="s">
         <v>722</v>
       </c>
       <c r="B298" t="s">
@@ -22760,7 +22760,7 @@
       </c>
     </row>
     <row r="299" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A299" s="31" t="s">
+      <c r="A299" s="29" t="s">
         <v>723</v>
       </c>
       <c r="B299" t="s">
@@ -22771,7 +22771,7 @@
       </c>
     </row>
     <row r="300" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A300" s="31" t="s">
+      <c r="A300" s="29" t="s">
         <v>724</v>
       </c>
       <c r="B300" t="s">
@@ -22782,7 +22782,7 @@
       </c>
     </row>
     <row r="301" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A301" s="31" t="s">
+      <c r="A301" s="29" t="s">
         <v>725</v>
       </c>
       <c r="B301" t="s">
@@ -22793,7 +22793,7 @@
       </c>
     </row>
     <row r="302" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A302" s="31" t="s">
+      <c r="A302" s="29" t="s">
         <v>726</v>
       </c>
       <c r="B302" t="s">
@@ -22804,7 +22804,7 @@
       </c>
     </row>
     <row r="303" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A303" s="31" t="s">
+      <c r="A303" s="29" t="s">
         <v>727</v>
       </c>
       <c r="B303" t="s">
@@ -22815,7 +22815,7 @@
       </c>
     </row>
     <row r="304" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A304" s="31" t="s">
+      <c r="A304" s="29" t="s">
         <v>728</v>
       </c>
       <c r="B304" t="s">
@@ -22826,7 +22826,7 @@
       </c>
     </row>
     <row r="305" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A305" s="31" t="s">
+      <c r="A305" s="29" t="s">
         <v>729</v>
       </c>
       <c r="B305" t="s">
@@ -22837,7 +22837,7 @@
       </c>
     </row>
     <row r="306" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A306" s="31" t="s">
+      <c r="A306" s="29" t="s">
         <v>730</v>
       </c>
       <c r="B306" t="s">
@@ -22848,7 +22848,7 @@
       </c>
     </row>
     <row r="307" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A307" s="31" t="s">
+      <c r="A307" s="29" t="s">
         <v>731</v>
       </c>
       <c r="B307" t="s">
@@ -22859,7 +22859,7 @@
       </c>
     </row>
     <row r="308" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A308" s="31" t="s">
+      <c r="A308" s="29" t="s">
         <v>732</v>
       </c>
       <c r="B308" t="s">
@@ -22870,7 +22870,7 @@
       </c>
     </row>
     <row r="309" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A309" s="31" t="s">
+      <c r="A309" s="29" t="s">
         <v>733</v>
       </c>
       <c r="B309" t="s">
@@ -22881,7 +22881,7 @@
       </c>
     </row>
     <row r="310" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A310" s="31" t="s">
+      <c r="A310" s="29" t="s">
         <v>734</v>
       </c>
       <c r="B310" t="s">
@@ -22892,7 +22892,7 @@
       </c>
     </row>
     <row r="311" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A311" s="31" t="s">
+      <c r="A311" s="29" t="s">
         <v>735</v>
       </c>
       <c r="B311" t="s">
@@ -22903,7 +22903,7 @@
       </c>
     </row>
     <row r="312" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A312" s="31" t="s">
+      <c r="A312" s="29" t="s">
         <v>736</v>
       </c>
       <c r="B312" t="s">
@@ -22914,7 +22914,7 @@
       </c>
     </row>
     <row r="313" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A313" s="31" t="s">
+      <c r="A313" s="29" t="s">
         <v>737</v>
       </c>
       <c r="B313" t="s">
@@ -22925,7 +22925,7 @@
       </c>
     </row>
     <row r="314" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A314" s="31" t="s">
+      <c r="A314" s="29" t="s">
         <v>738</v>
       </c>
       <c r="B314" t="s">
@@ -22936,10 +22936,10 @@
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="30"/>
+      <c r="A315" s="28"/>
     </row>
     <row r="316" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A316" s="31" t="s">
+      <c r="A316" s="29" t="s">
         <v>739</v>
       </c>
       <c r="B316" t="s">
@@ -22950,7 +22950,7 @@
       </c>
     </row>
     <row r="317" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A317" s="31" t="s">
+      <c r="A317" s="29" t="s">
         <v>740</v>
       </c>
       <c r="B317" t="s">
@@ -22961,7 +22961,7 @@
       </c>
     </row>
     <row r="318" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A318" s="31" t="s">
+      <c r="A318" s="29" t="s">
         <v>741</v>
       </c>
       <c r="B318" t="s">
@@ -22972,7 +22972,7 @@
       </c>
     </row>
     <row r="319" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A319" s="31" t="s">
+      <c r="A319" s="29" t="s">
         <v>742</v>
       </c>
       <c r="B319" t="s">
@@ -22983,7 +22983,7 @@
       </c>
     </row>
     <row r="320" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A320" s="31" t="s">
+      <c r="A320" s="29" t="s">
         <v>743</v>
       </c>
       <c r="B320" t="s">
@@ -22994,7 +22994,7 @@
       </c>
     </row>
     <row r="321" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A321" s="31" t="s">
+      <c r="A321" s="29" t="s">
         <v>744</v>
       </c>
       <c r="B321" t="s">
@@ -23005,7 +23005,7 @@
       </c>
     </row>
     <row r="322" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A322" s="31" t="s">
+      <c r="A322" s="29" t="s">
         <v>745</v>
       </c>
       <c r="B322" t="s">
@@ -23016,7 +23016,7 @@
       </c>
     </row>
     <row r="323" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A323" s="31" t="s">
+      <c r="A323" s="29" t="s">
         <v>746</v>
       </c>
       <c r="B323" t="s">
@@ -23027,7 +23027,7 @@
       </c>
     </row>
     <row r="324" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A324" s="31" t="s">
+      <c r="A324" s="29" t="s">
         <v>747</v>
       </c>
       <c r="B324" t="s">
@@ -23038,7 +23038,7 @@
       </c>
     </row>
     <row r="325" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A325" s="31" t="s">
+      <c r="A325" s="29" t="s">
         <v>748</v>
       </c>
       <c r="B325" t="s">
@@ -23049,7 +23049,7 @@
       </c>
     </row>
     <row r="326" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A326" s="31" t="s">
+      <c r="A326" s="29" t="s">
         <v>749</v>
       </c>
       <c r="B326" t="s">
@@ -23060,7 +23060,7 @@
       </c>
     </row>
     <row r="327" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A327" s="31" t="s">
+      <c r="A327" s="29" t="s">
         <v>750</v>
       </c>
       <c r="B327" t="s">
@@ -23071,7 +23071,7 @@
       </c>
     </row>
     <row r="328" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A328" s="31" t="s">
+      <c r="A328" s="29" t="s">
         <v>751</v>
       </c>
       <c r="B328" t="s">
@@ -23082,7 +23082,7 @@
       </c>
     </row>
     <row r="329" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A329" s="31" t="s">
+      <c r="A329" s="29" t="s">
         <v>752</v>
       </c>
       <c r="B329" t="s">
@@ -23093,7 +23093,7 @@
       </c>
     </row>
     <row r="330" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A330" s="31" t="s">
+      <c r="A330" s="29" t="s">
         <v>753</v>
       </c>
       <c r="B330" t="s">
@@ -23104,7 +23104,7 @@
       </c>
     </row>
     <row r="331" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A331" s="31" t="s">
+      <c r="A331" s="29" t="s">
         <v>754</v>
       </c>
       <c r="B331" t="s">
@@ -23115,7 +23115,7 @@
       </c>
     </row>
     <row r="332" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A332" s="31" t="s">
+      <c r="A332" s="29" t="s">
         <v>755</v>
       </c>
       <c r="B332" t="s">
@@ -23126,7 +23126,7 @@
       </c>
     </row>
     <row r="333" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A333" s="31" t="s">
+      <c r="A333" s="29" t="s">
         <v>756</v>
       </c>
       <c r="B333" t="s">
@@ -23137,7 +23137,7 @@
       </c>
     </row>
     <row r="334" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A334" s="31" t="s">
+      <c r="A334" s="29" t="s">
         <v>757</v>
       </c>
       <c r="B334" t="s">
@@ -23148,7 +23148,7 @@
       </c>
     </row>
     <row r="335" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A335" s="31" t="s">
+      <c r="A335" s="29" t="s">
         <v>758</v>
       </c>
       <c r="B335" t="s">
@@ -23159,7 +23159,7 @@
       </c>
     </row>
     <row r="336" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A336" s="31" t="s">
+      <c r="A336" s="29" t="s">
         <v>759</v>
       </c>
       <c r="B336" t="s">
@@ -23170,7 +23170,7 @@
       </c>
     </row>
     <row r="337" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A337" s="31" t="s">
+      <c r="A337" s="29" t="s">
         <v>760</v>
       </c>
       <c r="B337" t="s">
@@ -23181,7 +23181,7 @@
       </c>
     </row>
     <row r="338" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A338" s="31" t="s">
+      <c r="A338" s="29" t="s">
         <v>761</v>
       </c>
       <c r="B338" t="s">
@@ -23192,7 +23192,7 @@
       </c>
     </row>
     <row r="339" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A339" s="31" t="s">
+      <c r="A339" s="29" t="s">
         <v>762</v>
       </c>
       <c r="B339" t="s">
@@ -23203,10 +23203,10 @@
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" s="30"/>
+      <c r="A340" s="28"/>
     </row>
     <row r="341" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A341" s="31" t="s">
+      <c r="A341" s="29" t="s">
         <v>763</v>
       </c>
       <c r="B341" t="s">
@@ -23217,7 +23217,7 @@
       </c>
     </row>
     <row r="342" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A342" s="31" t="s">
+      <c r="A342" s="29" t="s">
         <v>764</v>
       </c>
       <c r="B342" t="s">
@@ -23228,7 +23228,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A343" s="31" t="s">
+      <c r="A343" s="29" t="s">
         <v>765</v>
       </c>
       <c r="B343" t="s">
@@ -23239,7 +23239,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A344" s="31" t="s">
+      <c r="A344" s="29" t="s">
         <v>766</v>
       </c>
       <c r="B344" t="s">
@@ -23250,7 +23250,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A345" s="31" t="s">
+      <c r="A345" s="29" t="s">
         <v>767</v>
       </c>
       <c r="B345" t="s">
@@ -23261,7 +23261,7 @@
       </c>
     </row>
     <row r="346" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A346" s="31" t="s">
+      <c r="A346" s="29" t="s">
         <v>768</v>
       </c>
       <c r="B346" t="s">
@@ -23272,7 +23272,7 @@
       </c>
     </row>
     <row r="347" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A347" s="31" t="s">
+      <c r="A347" s="29" t="s">
         <v>769</v>
       </c>
       <c r="B347" t="s">
@@ -23283,7 +23283,7 @@
       </c>
     </row>
     <row r="348" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A348" s="31" t="s">
+      <c r="A348" s="29" t="s">
         <v>770</v>
       </c>
       <c r="B348" t="s">
@@ -23294,7 +23294,7 @@
       </c>
     </row>
     <row r="349" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A349" s="31" t="s">
+      <c r="A349" s="29" t="s">
         <v>771</v>
       </c>
       <c r="B349" t="s">
@@ -23305,7 +23305,7 @@
       </c>
     </row>
     <row r="350" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A350" s="31" t="s">
+      <c r="A350" s="29" t="s">
         <v>772</v>
       </c>
       <c r="B350" t="s">
@@ -23316,7 +23316,7 @@
       </c>
     </row>
     <row r="351" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A351" s="31" t="s">
+      <c r="A351" s="29" t="s">
         <v>773</v>
       </c>
       <c r="B351" t="s">
@@ -23327,7 +23327,7 @@
       </c>
     </row>
     <row r="352" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A352" s="31" t="s">
+      <c r="A352" s="29" t="s">
         <v>774</v>
       </c>
       <c r="B352" t="s">
@@ -23338,7 +23338,7 @@
       </c>
     </row>
     <row r="353" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A353" s="31" t="s">
+      <c r="A353" s="29" t="s">
         <v>775</v>
       </c>
       <c r="B353" t="s">
@@ -23349,7 +23349,7 @@
       </c>
     </row>
     <row r="354" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A354" s="31" t="s">
+      <c r="A354" s="29" t="s">
         <v>776</v>
       </c>
       <c r="B354" t="s">
@@ -23360,7 +23360,7 @@
       </c>
     </row>
     <row r="355" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A355" s="31" t="s">
+      <c r="A355" s="29" t="s">
         <v>777</v>
       </c>
       <c r="B355" t="s">
@@ -23371,7 +23371,7 @@
       </c>
     </row>
     <row r="356" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A356" s="31" t="s">
+      <c r="A356" s="29" t="s">
         <v>778</v>
       </c>
       <c r="B356" t="s">
@@ -23382,7 +23382,7 @@
       </c>
     </row>
     <row r="357" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A357" s="31" t="s">
+      <c r="A357" s="29" t="s">
         <v>779</v>
       </c>
       <c r="B357" t="s">
@@ -23393,7 +23393,7 @@
       </c>
     </row>
     <row r="358" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A358" s="31" t="s">
+      <c r="A358" s="29" t="s">
         <v>780</v>
       </c>
       <c r="B358" t="s">
@@ -23404,7 +23404,7 @@
       </c>
     </row>
     <row r="359" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A359" s="31" t="s">
+      <c r="A359" s="29" t="s">
         <v>781</v>
       </c>
       <c r="B359" t="s">
@@ -23415,7 +23415,7 @@
       </c>
     </row>
     <row r="360" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A360" s="31" t="s">
+      <c r="A360" s="29" t="s">
         <v>782</v>
       </c>
       <c r="B360" t="s">
@@ -23426,7 +23426,7 @@
       </c>
     </row>
     <row r="361" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A361" s="31" t="s">
+      <c r="A361" s="29" t="s">
         <v>783</v>
       </c>
       <c r="B361" t="s">
@@ -23437,10 +23437,10 @@
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" s="30"/>
+      <c r="A362" s="28"/>
     </row>
     <row r="363" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A363" s="31" t="s">
+      <c r="A363" s="29" t="s">
         <v>784</v>
       </c>
       <c r="B363" t="s">
@@ -23451,7 +23451,7 @@
       </c>
     </row>
     <row r="364" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A364" s="31" t="s">
+      <c r="A364" s="29" t="s">
         <v>785</v>
       </c>
       <c r="B364" t="s">
@@ -23462,7 +23462,7 @@
       </c>
     </row>
     <row r="365" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A365" s="31" t="s">
+      <c r="A365" s="29" t="s">
         <v>786</v>
       </c>
       <c r="B365" t="s">
@@ -23473,7 +23473,7 @@
       </c>
     </row>
     <row r="366" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A366" s="31" t="s">
+      <c r="A366" s="29" t="s">
         <v>787</v>
       </c>
       <c r="B366" t="s">
@@ -23484,7 +23484,7 @@
       </c>
     </row>
     <row r="367" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A367" s="31" t="s">
+      <c r="A367" s="29" t="s">
         <v>788</v>
       </c>
       <c r="B367" t="s">
@@ -23495,7 +23495,7 @@
       </c>
     </row>
     <row r="368" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A368" s="31" t="s">
+      <c r="A368" s="29" t="s">
         <v>789</v>
       </c>
       <c r="B368" t="s">
@@ -23506,7 +23506,7 @@
       </c>
     </row>
     <row r="369" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A369" s="31" t="s">
+      <c r="A369" s="29" t="s">
         <v>790</v>
       </c>
       <c r="B369" t="s">
@@ -23517,7 +23517,7 @@
       </c>
     </row>
     <row r="370" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A370" s="31" t="s">
+      <c r="A370" s="29" t="s">
         <v>791</v>
       </c>
       <c r="B370" t="s">
@@ -23528,7 +23528,7 @@
       </c>
     </row>
     <row r="371" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A371" s="31" t="s">
+      <c r="A371" s="29" t="s">
         <v>792</v>
       </c>
       <c r="B371" t="s">
@@ -23539,7 +23539,7 @@
       </c>
     </row>
     <row r="372" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A372" s="31" t="s">
+      <c r="A372" s="29" t="s">
         <v>793</v>
       </c>
       <c r="B372" t="s">
@@ -23550,7 +23550,7 @@
       </c>
     </row>
     <row r="373" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A373" s="31" t="s">
+      <c r="A373" s="29" t="s">
         <v>794</v>
       </c>
       <c r="B373" t="s">
@@ -23561,7 +23561,7 @@
       </c>
     </row>
     <row r="374" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A374" s="31" t="s">
+      <c r="A374" s="29" t="s">
         <v>795</v>
       </c>
       <c r="B374" t="s">
@@ -23572,7 +23572,7 @@
       </c>
     </row>
     <row r="375" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A375" s="31" t="s">
+      <c r="A375" s="29" t="s">
         <v>796</v>
       </c>
       <c r="B375" t="s">
@@ -23583,7 +23583,7 @@
       </c>
     </row>
     <row r="376" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A376" s="31" t="s">
+      <c r="A376" s="29" t="s">
         <v>797</v>
       </c>
       <c r="B376" t="s">
@@ -23594,7 +23594,7 @@
       </c>
     </row>
     <row r="377" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A377" s="31" t="s">
+      <c r="A377" s="29" t="s">
         <v>798</v>
       </c>
       <c r="B377" t="s">
@@ -23605,10 +23605,10 @@
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" s="30"/>
+      <c r="A378" s="28"/>
     </row>
     <row r="379" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A379" s="31" t="s">
+      <c r="A379" s="29" t="s">
         <v>799</v>
       </c>
       <c r="B379" t="s">
@@ -23619,7 +23619,7 @@
       </c>
     </row>
     <row r="380" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A380" s="31" t="s">
+      <c r="A380" s="29" t="s">
         <v>800</v>
       </c>
       <c r="B380" t="s">
@@ -23630,7 +23630,7 @@
       </c>
     </row>
     <row r="381" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A381" s="31" t="s">
+      <c r="A381" s="29" t="s">
         <v>801</v>
       </c>
       <c r="B381" t="s">
@@ -23641,7 +23641,7 @@
       </c>
     </row>
     <row r="382" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A382" s="31" t="s">
+      <c r="A382" s="29" t="s">
         <v>802</v>
       </c>
       <c r="B382" t="s">
@@ -23652,7 +23652,7 @@
       </c>
     </row>
     <row r="383" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A383" s="31" t="s">
+      <c r="A383" s="29" t="s">
         <v>803</v>
       </c>
       <c r="B383" t="s">
@@ -23663,7 +23663,7 @@
       </c>
     </row>
     <row r="384" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A384" s="31" t="s">
+      <c r="A384" s="29" t="s">
         <v>804</v>
       </c>
       <c r="B384" t="s">
@@ -23674,7 +23674,7 @@
       </c>
     </row>
     <row r="385" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A385" s="31" t="s">
+      <c r="A385" s="29" t="s">
         <v>805</v>
       </c>
       <c r="B385" t="s">
@@ -23685,7 +23685,7 @@
       </c>
     </row>
     <row r="386" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A386" s="31" t="s">
+      <c r="A386" s="29" t="s">
         <v>806</v>
       </c>
       <c r="B386" t="s">
@@ -23696,7 +23696,7 @@
       </c>
     </row>
     <row r="387" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A387" s="31" t="s">
+      <c r="A387" s="29" t="s">
         <v>807</v>
       </c>
       <c r="B387" t="s">
@@ -23707,7 +23707,7 @@
       </c>
     </row>
     <row r="388" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A388" s="31" t="s">
+      <c r="A388" s="29" t="s">
         <v>808</v>
       </c>
       <c r="B388" t="s">
@@ -23718,7 +23718,7 @@
       </c>
     </row>
     <row r="389" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A389" s="31" t="s">
+      <c r="A389" s="29" t="s">
         <v>809</v>
       </c>
       <c r="B389" t="s">
@@ -23729,7 +23729,7 @@
       </c>
     </row>
     <row r="390" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A390" s="31" t="s">
+      <c r="A390" s="29" t="s">
         <v>810</v>
       </c>
       <c r="B390" t="s">
@@ -23740,7 +23740,7 @@
       </c>
     </row>
     <row r="391" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A391" s="31" t="s">
+      <c r="A391" s="29" t="s">
         <v>811</v>
       </c>
       <c r="B391" t="s">
@@ -23751,7 +23751,7 @@
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A392" s="31" t="s">
+      <c r="A392" s="29" t="s">
         <v>812</v>
       </c>
       <c r="B392" t="s">
@@ -23762,7 +23762,7 @@
       </c>
     </row>
     <row r="393" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A393" s="31" t="s">
+      <c r="A393" s="29" t="s">
         <v>813</v>
       </c>
       <c r="B393" t="s">
@@ -23773,7 +23773,7 @@
       </c>
     </row>
     <row r="394" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A394" s="31" t="s">
+      <c r="A394" s="29" t="s">
         <v>814</v>
       </c>
       <c r="B394" t="s">
@@ -23784,7 +23784,7 @@
       </c>
     </row>
     <row r="395" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A395" s="31" t="s">
+      <c r="A395" s="29" t="s">
         <v>815</v>
       </c>
       <c r="B395" t="s">
@@ -23795,7 +23795,7 @@
       </c>
     </row>
     <row r="396" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A396" s="31" t="s">
+      <c r="A396" s="29" t="s">
         <v>816</v>
       </c>
       <c r="B396" t="s">
@@ -23806,7 +23806,7 @@
       </c>
     </row>
     <row r="397" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A397" s="31" t="s">
+      <c r="A397" s="29" t="s">
         <v>817</v>
       </c>
       <c r="B397" t="s">
@@ -23817,7 +23817,7 @@
       </c>
     </row>
     <row r="398" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A398" s="31" t="s">
+      <c r="A398" s="29" t="s">
         <v>818</v>
       </c>
       <c r="B398" t="s">
@@ -23828,7 +23828,7 @@
       </c>
     </row>
     <row r="399" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A399" s="31" t="s">
+      <c r="A399" s="29" t="s">
         <v>819</v>
       </c>
       <c r="B399" t="s">
@@ -23839,7 +23839,7 @@
       </c>
     </row>
     <row r="400" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A400" s="31" t="s">
+      <c r="A400" s="29" t="s">
         <v>820</v>
       </c>
       <c r="B400" t="s">
@@ -23850,7 +23850,7 @@
       </c>
     </row>
     <row r="401" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A401" s="31" t="s">
+      <c r="A401" s="29" t="s">
         <v>821</v>
       </c>
       <c r="B401" t="s">
@@ -23861,7 +23861,7 @@
       </c>
     </row>
     <row r="402" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A402" s="31" t="s">
+      <c r="A402" s="29" t="s">
         <v>822</v>
       </c>
       <c r="B402" t="s">
@@ -23872,7 +23872,7 @@
       </c>
     </row>
     <row r="403" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A403" s="31" t="s">
+      <c r="A403" s="29" t="s">
         <v>823</v>
       </c>
       <c r="B403" t="s">
@@ -23883,7 +23883,7 @@
       </c>
     </row>
     <row r="404" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A404" s="31" t="s">
+      <c r="A404" s="29" t="s">
         <v>824</v>
       </c>
       <c r="B404" t="s">
@@ -23894,7 +23894,7 @@
       </c>
     </row>
     <row r="405" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A405" s="31" t="s">
+      <c r="A405" s="29" t="s">
         <v>825</v>
       </c>
       <c r="B405" t="s">
@@ -23905,10 +23905,10 @@
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="30"/>
+      <c r="A406" s="28"/>
     </row>
     <row r="407" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A407" s="31" t="s">
+      <c r="A407" s="29" t="s">
         <v>826</v>
       </c>
       <c r="B407" t="s">
@@ -23919,7 +23919,7 @@
       </c>
     </row>
     <row r="408" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A408" s="31" t="s">
+      <c r="A408" s="29" t="s">
         <v>827</v>
       </c>
       <c r="B408" t="s">
@@ -23930,7 +23930,7 @@
       </c>
     </row>
     <row r="409" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A409" s="31" t="s">
+      <c r="A409" s="29" t="s">
         <v>828</v>
       </c>
       <c r="B409" t="s">
@@ -23941,7 +23941,7 @@
       </c>
     </row>
     <row r="410" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A410" s="31" t="s">
+      <c r="A410" s="29" t="s">
         <v>829</v>
       </c>
       <c r="B410" t="s">
@@ -23952,7 +23952,7 @@
       </c>
     </row>
     <row r="411" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A411" s="31" t="s">
+      <c r="A411" s="29" t="s">
         <v>830</v>
       </c>
       <c r="B411" t="s">
@@ -23963,7 +23963,7 @@
       </c>
     </row>
     <row r="412" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A412" s="31" t="s">
+      <c r="A412" s="29" t="s">
         <v>831</v>
       </c>
       <c r="B412" t="s">
@@ -23974,7 +23974,7 @@
       </c>
     </row>
     <row r="413" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A413" s="31" t="s">
+      <c r="A413" s="29" t="s">
         <v>832</v>
       </c>
       <c r="B413" t="s">
@@ -23985,7 +23985,7 @@
       </c>
     </row>
     <row r="414" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A414" s="31" t="s">
+      <c r="A414" s="29" t="s">
         <v>833</v>
       </c>
       <c r="B414" t="s">
@@ -23996,7 +23996,7 @@
       </c>
     </row>
     <row r="415" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A415" s="31" t="s">
+      <c r="A415" s="29" t="s">
         <v>834</v>
       </c>
       <c r="B415" t="s">
@@ -24007,7 +24007,7 @@
       </c>
     </row>
     <row r="416" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A416" s="31" t="s">
+      <c r="A416" s="29" t="s">
         <v>835</v>
       </c>
       <c r="B416" t="s">
@@ -24018,7 +24018,7 @@
       </c>
     </row>
     <row r="417" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A417" s="31" t="s">
+      <c r="A417" s="29" t="s">
         <v>836</v>
       </c>
       <c r="B417" t="s">
@@ -24029,7 +24029,7 @@
       </c>
     </row>
     <row r="418" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A418" s="31" t="s">
+      <c r="A418" s="29" t="s">
         <v>837</v>
       </c>
       <c r="B418" t="s">
@@ -24040,7 +24040,7 @@
       </c>
     </row>
     <row r="419" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A419" s="31" t="s">
+      <c r="A419" s="29" t="s">
         <v>838</v>
       </c>
       <c r="B419" t="s">
@@ -24051,7 +24051,7 @@
       </c>
     </row>
     <row r="420" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A420" s="31" t="s">
+      <c r="A420" s="29" t="s">
         <v>839</v>
       </c>
       <c r="B420" t="s">
@@ -24062,7 +24062,7 @@
       </c>
     </row>
     <row r="421" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A421" s="31" t="s">
+      <c r="A421" s="29" t="s">
         <v>840</v>
       </c>
       <c r="B421" t="s">
@@ -24073,7 +24073,7 @@
       </c>
     </row>
     <row r="422" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A422" s="31" t="s">
+      <c r="A422" s="29" t="s">
         <v>841</v>
       </c>
       <c r="B422" t="s">
@@ -24084,7 +24084,7 @@
       </c>
     </row>
     <row r="423" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A423" s="31" t="s">
+      <c r="A423" s="29" t="s">
         <v>842</v>
       </c>
       <c r="B423" t="s">
@@ -24095,7 +24095,7 @@
       </c>
     </row>
     <row r="424" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A424" s="31" t="s">
+      <c r="A424" s="29" t="s">
         <v>843</v>
       </c>
       <c r="B424" t="s">
@@ -24106,7 +24106,7 @@
       </c>
     </row>
     <row r="425" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A425" s="31" t="s">
+      <c r="A425" s="29" t="s">
         <v>844</v>
       </c>
       <c r="B425" t="s">
@@ -24117,7 +24117,7 @@
       </c>
     </row>
     <row r="426" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A426" s="31" t="s">
+      <c r="A426" s="29" t="s">
         <v>845</v>
       </c>
       <c r="B426" t="s">
@@ -24128,7 +24128,7 @@
       </c>
     </row>
     <row r="427" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A427" s="31" t="s">
+      <c r="A427" s="29" t="s">
         <v>846</v>
       </c>
       <c r="B427" t="s">
@@ -24139,82 +24139,82 @@
       </c>
     </row>
     <row r="428" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A428" s="31"/>
+      <c r="A428" s="29"/>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" s="30"/>
+      <c r="A429" s="28"/>
     </row>
     <row r="430" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A430" s="31"/>
+      <c r="A430" s="29"/>
     </row>
     <row r="431" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A431" s="31"/>
+      <c r="A431" s="29"/>
     </row>
     <row r="432" spans="1:3" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A432" s="31"/>
+      <c r="A432" s="29"/>
     </row>
     <row r="433" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A433" s="31"/>
+      <c r="A433" s="29"/>
     </row>
     <row r="434" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A434" s="31"/>
+      <c r="A434" s="29"/>
     </row>
     <row r="435" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A435" s="31"/>
+      <c r="A435" s="29"/>
     </row>
     <row r="436" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A436" s="31"/>
+      <c r="A436" s="29"/>
     </row>
     <row r="437" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A437" s="31"/>
+      <c r="A437" s="29"/>
     </row>
     <row r="438" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A438" s="31"/>
+      <c r="A438" s="29"/>
     </row>
     <row r="439" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A439" s="31"/>
+      <c r="A439" s="29"/>
     </row>
     <row r="440" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A440" s="31"/>
+      <c r="A440" s="29"/>
     </row>
     <row r="441" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A441" s="31"/>
+      <c r="A441" s="29"/>
     </row>
     <row r="442" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A442" s="31"/>
+      <c r="A442" s="29"/>
     </row>
     <row r="443" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A443" s="31"/>
+      <c r="A443" s="29"/>
     </row>
     <row r="444" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A444" s="31"/>
+      <c r="A444" s="29"/>
     </row>
     <row r="445" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A445" s="31"/>
+      <c r="A445" s="29"/>
     </row>
     <row r="446" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A446" s="31"/>
+      <c r="A446" s="29"/>
     </row>
     <row r="447" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A447" s="31"/>
+      <c r="A447" s="29"/>
     </row>
     <row r="448" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A448" s="31"/>
+      <c r="A448" s="29"/>
     </row>
     <row r="449" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A449" s="31"/>
+      <c r="A449" s="29"/>
     </row>
     <row r="450" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A450" s="31"/>
+      <c r="A450" s="29"/>
     </row>
     <row r="451" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A451" s="31"/>
+      <c r="A451" s="29"/>
     </row>
     <row r="452" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A452" s="31"/>
+      <c r="A452" s="29"/>
     </row>
     <row r="453" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A453" s="31"/>
+      <c r="A453" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/book/src/doc/Libros.xlsx
+++ b/book/src/doc/Libros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\book\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F398F80F-437D-4FDF-BEEF-88617B7BAC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D25C17-0246-4315-B41D-25B1C97D6B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="5" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
-    <sheet name="Versiculos" sheetId="7" r:id="rId7"/>
-    <sheet name="Limpieza" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="9" r:id="rId7"/>
+    <sheet name="Versiculos" sheetId="7" r:id="rId8"/>
+    <sheet name="Limpieza" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1672">
   <si>
     <r>
       <t>to </t>
@@ -11212,6 +11213,51 @@
   </si>
   <si>
     <t xml:space="preserve">        "21": "Que la gracia del Señor Jesús sea con todos. ¡Amén"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Libro</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Ver</t>
+  </si>
+  <si>
+    <t>hasta</t>
+  </si>
+  <si>
+    <t>50_jn</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>qo</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>25_qo</t>
+  </si>
+  <si>
+    <t>28_si</t>
   </si>
 </sst>
 </file>
@@ -11712,6 +11758,55 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>25066</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>35092</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>496302</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>45389</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C06F15A-AA16-ED50-5305-109551CD2C4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5970671" y="35092"/>
+          <a:ext cx="3529263" cy="5534797"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
@@ -11735,7 +11830,7 @@
                   <a14:compatExt spid="_x0000_s8193"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000001200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000001200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11803,7 +11898,7 @@
                   <a14:compatExt spid="_x0000_s8198"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000006200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -17968,6 +18063,1628 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9159EC-82D3-41AA-9A2F-C77340E8D3D4}">
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+      <c r="I3">
+        <v>26</v>
+      </c>
+      <c r="L3" t="str">
+        <f>_xlfn.CONCAT("""",G3,"-c",H3,"-v",I3:K3,"""" )</f>
+        <v>"29_is-c40-v26"</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G4" t="s">
+        <v>343</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="L4" t="str">
+        <f>_xlfn.CONCAT("""",G4,"-c",H4,"-v",I4:K4,"""" )</f>
+        <v>"56_ef-c3-v9"</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" ref="L5:L13" si="0">_xlfn.CONCAT("""",G5,"-c",H5,"-v",I5:K5,"""" )</f>
+        <v>"65_hb-c1-v2"</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>"65_hb-c11-v3"</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>"-c-v"</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>"23_sal-c8-v4"</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" t="s">
+        <v>285</v>
+      </c>
+      <c r="G9" t="s">
+        <v>318</v>
+      </c>
+      <c r="H9">
+        <v>42</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>"29_is-c42-v5"</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H10">
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>"29_is-c44-v24"</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G11" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11">
+        <v>45</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>"29_is-c45-v18"</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" t="s">
+        <v>288</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>"50_jn-c1-v1"</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D13" t="s">
+        <v>289</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1663</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>"-c-v"</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
+        <v>290</v>
+      </c>
+      <c r="G14" t="s">
+        <v>311</v>
+      </c>
+      <c r="H14">
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="L14" t="str">
+        <f>_xlfn.CONCAT("""",G14,"-c",H14,"-v",I14:K14,"""," )</f>
+        <v>"22_jb-c26-v7",</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" t="s">
+        <v>304</v>
+      </c>
+      <c r="G15" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15">
+        <v>104</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" ref="L15:L78" si="1">_xlfn.CONCAT("""",G15,"-c",H15,"-v",I15:K15,"""," )</f>
+        <v>"23_sal-c104-v30",</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" t="s">
+        <v>305</v>
+      </c>
+      <c r="G16" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16">
+        <v>12</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K16">
+        <v>14</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="1"/>
+        <v>"29_is-c40-v12-14",</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
+        <v>306</v>
+      </c>
+      <c r="G17" t="s">
+        <v>319</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>23</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="1"/>
+        <v>"30_jr-c4-v23",</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G18" t="s">
+        <v>300</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="1"/>
+        <v>"68_2p-c3-v5",</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" t="s">
+        <v>291</v>
+      </c>
+      <c r="G20" t="s">
+        <v>312</v>
+      </c>
+      <c r="H20">
+        <v>33</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K20">
+        <v>9</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="1"/>
+        <v>"23_sal-c33-v6.9",</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" t="s">
+        <v>292</v>
+      </c>
+      <c r="G21" t="s">
+        <v>316</v>
+      </c>
+      <c r="H21">
+        <v>7</v>
+      </c>
+      <c r="I21">
+        <v>26</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="1"/>
+        <v>"27_sab-c7-v26",</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" t="s">
+        <v>318</v>
+      </c>
+      <c r="H22">
+        <v>60</v>
+      </c>
+      <c r="I22">
+        <v>19</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="1"/>
+        <v>"29_is-c60-v19",</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" t="s">
+        <v>312</v>
+      </c>
+      <c r="G23" t="s">
+        <v>294</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="1"/>
+        <v>"54_2co-c4-v6",</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" t="s">
+        <v>313</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1667</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1670</v>
+      </c>
+      <c r="G25" t="s">
+        <v>277</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="1"/>
+        <v>"01_gn-c3-v6",</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" t="s">
+        <v>315</v>
+      </c>
+      <c r="G26" t="s">
+        <v>278</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="1"/>
+        <v>"02_ex-c2-v2",</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" t="s">
+        <v>316</v>
+      </c>
+      <c r="G27" t="s">
+        <v>314</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="1"/>
+        <v>"25_ecl-c-v",</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1671</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" t="s">
+        <v>318</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" t="s">
+        <v>319</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" t="s">
+        <v>320</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" t="s">
+        <v>321</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" t="s">
+        <v>322</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D34" t="s">
+        <v>323</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" t="s">
+        <v>324</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" t="s">
+        <v>247</v>
+      </c>
+      <c r="D36" t="s">
+        <v>325</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" t="s">
+        <v>326</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" t="s">
+        <v>327</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>216</v>
+      </c>
+      <c r="D39" t="s">
+        <v>328</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" t="s">
+        <v>250</v>
+      </c>
+      <c r="D40" t="s">
+        <v>329</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>172</v>
+      </c>
+      <c r="C41" t="s">
+        <v>251</v>
+      </c>
+      <c r="D41" t="s">
+        <v>330</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>173</v>
+      </c>
+      <c r="C42" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" t="s">
+        <v>331</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D43" t="s">
+        <v>332</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" t="s">
+        <v>254</v>
+      </c>
+      <c r="D44" t="s">
+        <v>333</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" t="s">
+        <v>255</v>
+      </c>
+      <c r="D45" t="s">
+        <v>334</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" t="s">
+        <v>218</v>
+      </c>
+      <c r="D46" t="s">
+        <v>335</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" t="s">
+        <v>336</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" t="s">
+        <v>256</v>
+      </c>
+      <c r="D48" t="s">
+        <v>337</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" t="s">
+        <v>338</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1662</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D51" t="s">
+        <v>340</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52" t="s">
+        <v>341</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" t="s">
+        <v>258</v>
+      </c>
+      <c r="D53" t="s">
+        <v>293</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" t="s">
+        <v>259</v>
+      </c>
+      <c r="D54" t="s">
+        <v>294</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" t="s">
+        <v>260</v>
+      </c>
+      <c r="D55" t="s">
+        <v>342</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C56" t="s">
+        <v>261</v>
+      </c>
+      <c r="D56" t="s">
+        <v>343</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" t="s">
+        <v>262</v>
+      </c>
+      <c r="D57" t="s">
+        <v>344</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" t="s">
+        <v>345</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
+        <v>263</v>
+      </c>
+      <c r="D59" t="s">
+        <v>295</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D60" t="s">
+        <v>296</v>
+      </c>
+      <c r="L60" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>192</v>
+      </c>
+      <c r="C61" t="s">
+        <v>265</v>
+      </c>
+      <c r="D61" t="s">
+        <v>297</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" t="s">
+        <v>266</v>
+      </c>
+      <c r="D62" t="s">
+        <v>298</v>
+      </c>
+      <c r="L62" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" t="s">
+        <v>267</v>
+      </c>
+      <c r="D63" t="s">
+        <v>346</v>
+      </c>
+      <c r="L63" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" t="s">
+        <v>268</v>
+      </c>
+      <c r="D64" t="s">
+        <v>347</v>
+      </c>
+      <c r="L64" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" t="s">
+        <v>217</v>
+      </c>
+      <c r="D65" t="s">
+        <v>348</v>
+      </c>
+      <c r="L65" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" t="s">
+        <v>349</v>
+      </c>
+      <c r="L66" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" t="s">
+        <v>299</v>
+      </c>
+      <c r="L67" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>199</v>
+      </c>
+      <c r="C68" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" t="s">
+        <v>300</v>
+      </c>
+      <c r="L68" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" t="s">
+        <v>272</v>
+      </c>
+      <c r="D69" t="s">
+        <v>301</v>
+      </c>
+      <c r="L69" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>201</v>
+      </c>
+      <c r="C70" t="s">
+        <v>273</v>
+      </c>
+      <c r="D70" t="s">
+        <v>302</v>
+      </c>
+      <c r="L70" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>202</v>
+      </c>
+      <c r="C71" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" t="s">
+        <v>303</v>
+      </c>
+      <c r="L71" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" t="s">
+        <v>275</v>
+      </c>
+      <c r="D72" t="s">
+        <v>309</v>
+      </c>
+      <c r="L72" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" t="s">
+        <v>276</v>
+      </c>
+      <c r="D73" t="s">
+        <v>310</v>
+      </c>
+      <c r="L73" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L74" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L75" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L76" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L77" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L78" t="str">
+        <f t="shared" si="1"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L79" t="str">
+        <f t="shared" ref="L79:L85" si="2">_xlfn.CONCAT("""",G79,"-c",H79,"-v",I79:K79,"""," )</f>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L80" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="81" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L81" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="82" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L82" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="83" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L83" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="84" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L84" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+    <row r="85" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L85" t="str">
+        <f t="shared" si="2"/>
+        <v>"-c-v",</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G85" xr:uid="{FF4BFE4F-B1E7-4AC1-ACE0-13C3DE4D4678}">
+      <formula1>$D:$D</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C14ACC7-C8B5-44A2-B83D-EE980EA22816}">
   <sheetPr codeName="Sheet7">
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -19605,7 +21322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE78A61-B89A-4E11-A893-87E9D739AD96}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C453"/>
